--- a/inputs/products.xlsx
+++ b/inputs/products.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5940"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9396"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="Parça Süre Katsayı" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$282</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$2</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2850" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2018" uniqueCount="434">
   <si>
     <t>product_id</t>
   </si>
@@ -1284,210 +1284,6 @@
     <t>P260</t>
   </si>
   <si>
-    <t>P261</t>
-  </si>
-  <si>
-    <t>P262</t>
-  </si>
-  <si>
-    <t>P263</t>
-  </si>
-  <si>
-    <t>P264</t>
-  </si>
-  <si>
-    <t>P265</t>
-  </si>
-  <si>
-    <t>P266</t>
-  </si>
-  <si>
-    <t>P267</t>
-  </si>
-  <si>
-    <t>P268</t>
-  </si>
-  <si>
-    <t>P269</t>
-  </si>
-  <si>
-    <t>P287</t>
-  </si>
-  <si>
-    <t>P288</t>
-  </si>
-  <si>
-    <t>P290</t>
-  </si>
-  <si>
-    <t>P291</t>
-  </si>
-  <si>
-    <t>P292</t>
-  </si>
-  <si>
-    <t>P293</t>
-  </si>
-  <si>
-    <t>P294</t>
-  </si>
-  <si>
-    <t>P295</t>
-  </si>
-  <si>
-    <t>P296</t>
-  </si>
-  <si>
-    <t>P297</t>
-  </si>
-  <si>
-    <t>P298</t>
-  </si>
-  <si>
-    <t>P299</t>
-  </si>
-  <si>
-    <t>P300</t>
-  </si>
-  <si>
-    <t>P301</t>
-  </si>
-  <si>
-    <t>P324</t>
-  </si>
-  <si>
-    <t>P326</t>
-  </si>
-  <si>
-    <t>P327</t>
-  </si>
-  <si>
-    <t>P328</t>
-  </si>
-  <si>
-    <t>P329</t>
-  </si>
-  <si>
-    <t>P330</t>
-  </si>
-  <si>
-    <t>P331</t>
-  </si>
-  <si>
-    <t>P332</t>
-  </si>
-  <si>
-    <t>P333</t>
-  </si>
-  <si>
-    <t>P334</t>
-  </si>
-  <si>
-    <t>P335</t>
-  </si>
-  <si>
-    <t>P336</t>
-  </si>
-  <si>
-    <t>P337</t>
-  </si>
-  <si>
-    <t>P338</t>
-  </si>
-  <si>
-    <t>P339</t>
-  </si>
-  <si>
-    <t>P340</t>
-  </si>
-  <si>
-    <t>P341</t>
-  </si>
-  <si>
-    <t>P342</t>
-  </si>
-  <si>
-    <t>P343</t>
-  </si>
-  <si>
-    <t>P344</t>
-  </si>
-  <si>
-    <t>P345</t>
-  </si>
-  <si>
-    <t>P346</t>
-  </si>
-  <si>
-    <t>P347</t>
-  </si>
-  <si>
-    <t>P348</t>
-  </si>
-  <si>
-    <t>P349</t>
-  </si>
-  <si>
-    <t>P350</t>
-  </si>
-  <si>
-    <t>P351</t>
-  </si>
-  <si>
-    <t>P352</t>
-  </si>
-  <si>
-    <t>P353</t>
-  </si>
-  <si>
-    <t>P354</t>
-  </si>
-  <si>
-    <t>P355</t>
-  </si>
-  <si>
-    <t>P356</t>
-  </si>
-  <si>
-    <t>P357</t>
-  </si>
-  <si>
-    <t>P358</t>
-  </si>
-  <si>
-    <t>P359</t>
-  </si>
-  <si>
-    <t>P360</t>
-  </si>
-  <si>
-    <t>P361</t>
-  </si>
-  <si>
-    <t>P362</t>
-  </si>
-  <si>
-    <t>P363</t>
-  </si>
-  <si>
-    <t>P364</t>
-  </si>
-  <si>
-    <t>P365</t>
-  </si>
-  <si>
-    <t>P367</t>
-  </si>
-  <si>
-    <t>P368</t>
-  </si>
-  <si>
-    <t>P369</t>
-  </si>
-  <si>
-    <t>P370</t>
-  </si>
-  <si>
     <t>N22</t>
   </si>
   <si>
@@ -1531,9 +1327,6 @@
   </si>
   <si>
     <t>Unload</t>
-  </si>
-  <si>
-    <t>*</t>
   </si>
 </sst>
 </file>
@@ -1543,7 +1336,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="hh:mm;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1559,6 +1352,10 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1568,7 +1365,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1591,11 +1388,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1608,11 +1418,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1917,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.6640625" bestFit="1" customWidth="1"/>
@@ -1931,6499 +1743,123 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D2" s="10">
+        <v>440</v>
+      </c>
+      <c r="E2" s="10">
+        <v>2</v>
+      </c>
+      <c r="F2" s="10">
+        <v>2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>3</v>
+      </c>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="D3" s="10">
+        <v>450</v>
+      </c>
+      <c r="E3" s="10">
+        <v>2</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D2" s="6">
-        <v>45782.302407407406</v>
-      </c>
-      <c r="E2" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C3" t="s">
-        <v>215</v>
-      </c>
-      <c r="D3" s="6">
-        <v>45782.303159722222</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G3">
+      <c r="C4" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D4" s="10">
+        <v>460</v>
+      </c>
+      <c r="E4" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D4" s="6">
-        <v>45782.303159722222</v>
-      </c>
-      <c r="E4" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F4" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G4">
+      <c r="F4" s="10">
         <v>2</v>
       </c>
+      <c r="G4" s="10">
+        <v>2</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>405</v>
-      </c>
-      <c r="B5" t="s">
-        <v>213</v>
-      </c>
-      <c r="C5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="6">
-        <v>45782.303159722222</v>
-      </c>
-      <c r="E5" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F5" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G5">
+      <c r="A5" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="D5" s="10">
+        <v>470</v>
+      </c>
+      <c r="E5" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>211</v>
-      </c>
-      <c r="C6" t="s">
-        <v>214</v>
-      </c>
-      <c r="D6" s="6">
-        <v>45782.327777777777</v>
-      </c>
-      <c r="E6" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B7" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D7" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E7" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F7" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G7">
+      <c r="F5" s="10">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" t="s">
-        <v>213</v>
-      </c>
-      <c r="C8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F8" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>121</v>
-      </c>
-      <c r="B9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C9" t="s">
-        <v>216</v>
-      </c>
-      <c r="D9" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F9" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" t="s">
-        <v>211</v>
-      </c>
-      <c r="D10" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>394</v>
-      </c>
-      <c r="B11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" t="s">
-        <v>216</v>
-      </c>
-      <c r="D11" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>398</v>
-      </c>
-      <c r="B12" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" t="s">
-        <v>216</v>
-      </c>
-      <c r="D12" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>399</v>
-      </c>
-      <c r="B13" t="s">
-        <v>213</v>
-      </c>
-      <c r="C13" t="s">
-        <v>216</v>
-      </c>
-      <c r="D13" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>118</v>
-      </c>
-      <c r="B14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C14" t="s">
-        <v>216</v>
-      </c>
-      <c r="D14" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F14" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>143</v>
-      </c>
-      <c r="B15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>213</v>
-      </c>
-      <c r="C16" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" t="s">
-        <v>213</v>
-      </c>
-      <c r="C17" t="s">
-        <v>216</v>
-      </c>
-      <c r="D17" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>98</v>
-      </c>
-      <c r="B18" t="s">
-        <v>213</v>
-      </c>
-      <c r="C18" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F18" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>166</v>
-      </c>
-      <c r="B19" t="s">
-        <v>213</v>
-      </c>
-      <c r="C19" t="s">
-        <v>216</v>
-      </c>
-      <c r="D19" s="6">
-        <v>45782.332384259258</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F19" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>457</v>
-      </c>
-      <c r="B20" t="s">
-        <v>207</v>
-      </c>
-      <c r="C20" t="s">
-        <v>211</v>
-      </c>
-      <c r="D20" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F20" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>458</v>
-      </c>
-      <c r="B21" t="s">
-        <v>212</v>
-      </c>
-      <c r="C21" t="s">
-        <v>211</v>
-      </c>
-      <c r="D21" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>459</v>
-      </c>
-      <c r="B22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C22" t="s">
-        <v>211</v>
-      </c>
-      <c r="D22" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F22" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>460</v>
-      </c>
-      <c r="B23" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F23" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>461</v>
-      </c>
-      <c r="B24" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" t="s">
-        <v>213</v>
-      </c>
-      <c r="D24" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F24" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>462</v>
-      </c>
-      <c r="B25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C25" t="s">
-        <v>214</v>
-      </c>
-      <c r="D25" s="6">
-        <v>45782.373784722222</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F25" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" t="s">
-        <v>211</v>
-      </c>
-      <c r="C26" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="6">
-        <v>45782.398946759262</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F26" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>198</v>
-      </c>
-      <c r="B27" t="s">
-        <v>211</v>
-      </c>
-      <c r="C27" t="s">
-        <v>214</v>
-      </c>
-      <c r="D27" s="6">
-        <v>45782.398946759262</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F27" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="D28" s="10">
-        <v>45782.399745370371</v>
-      </c>
-      <c r="E28" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="F28" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G28" s="9">
-        <v>2</v>
-      </c>
-      <c r="H28" s="9"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>220</v>
-      </c>
-      <c r="D29" s="10">
-        <v>45782.400439814817</v>
-      </c>
-      <c r="E29" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="F29" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G29" s="9">
-        <v>2</v>
-      </c>
-      <c r="H29" s="9"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="10">
-        <v>45782.401180555556</v>
-      </c>
-      <c r="E30" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="F30" s="11">
-        <v>0.1</v>
-      </c>
-      <c r="G30" s="9">
-        <v>2</v>
-      </c>
-      <c r="H30" s="9"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>428</v>
-      </c>
-      <c r="B31" t="s">
-        <v>212</v>
-      </c>
-      <c r="C31" t="s">
-        <v>213</v>
-      </c>
-      <c r="D31" s="6">
-        <v>45782.410451388889</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F31" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" t="s">
-        <v>212</v>
-      </c>
-      <c r="C32" t="s">
-        <v>213</v>
-      </c>
-      <c r="D32" s="6">
-        <v>45782.410451388889</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F32" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>112</v>
-      </c>
-      <c r="B33" t="s">
-        <v>214</v>
-      </c>
-      <c r="C33" t="s">
-        <v>211</v>
-      </c>
-      <c r="D33" s="6">
-        <v>45782.444097222222</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F33" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>201</v>
-      </c>
-      <c r="B34" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" t="s">
-        <v>214</v>
-      </c>
-      <c r="D34" s="6">
-        <v>45782.444224537037</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F34" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>483</v>
-      </c>
-      <c r="B35" t="s">
-        <v>214</v>
-      </c>
-      <c r="C35" t="s">
-        <v>216</v>
-      </c>
-      <c r="D35" s="6">
-        <v>45782.455949074072</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F35" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>479</v>
-      </c>
-      <c r="B36" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" t="s">
-        <v>214</v>
-      </c>
-      <c r="D36" s="6">
-        <v>45782.487662037034</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F36" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>480</v>
-      </c>
-      <c r="B37" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" t="s">
-        <v>214</v>
-      </c>
-      <c r="D37" s="6">
-        <v>45782.487662037034</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F37" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>445</v>
-      </c>
-      <c r="B38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D38" s="6">
-        <v>45782.487858796296</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F38" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" t="s">
-        <v>216</v>
-      </c>
-      <c r="D39" s="6">
-        <v>45782.502847222226</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F39" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" t="s">
-        <v>211</v>
-      </c>
-      <c r="C40" t="s">
-        <v>213</v>
-      </c>
-      <c r="D40" s="6">
-        <v>45782.526956018519</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F40" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>211</v>
-      </c>
-      <c r="C41" t="s">
-        <v>213</v>
-      </c>
-      <c r="D41" s="6">
-        <v>45782.526956018519</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F41" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>148</v>
-      </c>
-      <c r="B42" t="s">
-        <v>211</v>
-      </c>
-      <c r="C42" t="s">
-        <v>216</v>
-      </c>
-      <c r="D42" s="6">
-        <v>45782.527141203704</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F42" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>125</v>
-      </c>
-      <c r="B43" t="s">
-        <v>211</v>
-      </c>
-      <c r="C43" t="s">
-        <v>214</v>
-      </c>
-      <c r="D43" s="6">
-        <v>45782.532743055555</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F43" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>429</v>
-      </c>
-      <c r="B44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" t="s">
-        <v>211</v>
-      </c>
-      <c r="D44" s="6">
-        <v>45782.534733796296</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F44" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>430</v>
-      </c>
-      <c r="B45" t="s">
-        <v>212</v>
-      </c>
-      <c r="C45" t="s">
-        <v>211</v>
-      </c>
-      <c r="D45" s="6">
-        <v>45782.534733796296</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F45" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>431</v>
-      </c>
-      <c r="B46" t="s">
-        <v>212</v>
-      </c>
-      <c r="C46" t="s">
-        <v>211</v>
-      </c>
-      <c r="D46" s="6">
-        <v>45782.534733796296</v>
-      </c>
-      <c r="E46" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F46" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>433</v>
-      </c>
-      <c r="B47" t="s">
-        <v>212</v>
-      </c>
-      <c r="C47" t="s">
-        <v>211</v>
-      </c>
-      <c r="D47" s="6">
-        <v>45782.534733796296</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F47" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>435</v>
-      </c>
-      <c r="B48" t="s">
-        <v>212</v>
-      </c>
-      <c r="C48" t="s">
-        <v>211</v>
-      </c>
-      <c r="D48" s="6">
-        <v>45782.534733796296</v>
-      </c>
-      <c r="E48" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F48" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>28</v>
-      </c>
-      <c r="B49" t="s">
-        <v>220</v>
-      </c>
-      <c r="C49" t="s">
-        <v>211</v>
-      </c>
-      <c r="D49" s="6">
-        <v>45782.548946759256</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F49" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>93</v>
-      </c>
-      <c r="B50" t="s">
-        <v>211</v>
-      </c>
-      <c r="C50" t="s">
-        <v>213</v>
-      </c>
-      <c r="D50" s="6">
-        <v>45782.570486111108</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F50" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>95</v>
-      </c>
-      <c r="B51" t="s">
-        <v>213</v>
-      </c>
-      <c r="C51" t="s">
-        <v>216</v>
-      </c>
-      <c r="D51" s="6">
-        <v>45782.583518518521</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F51" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52" t="s">
-        <v>213</v>
-      </c>
-      <c r="C52" t="s">
-        <v>216</v>
-      </c>
-      <c r="D52" s="6">
-        <v>45782.583518518521</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F52" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G52">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>407</v>
-      </c>
-      <c r="B53" t="s">
-        <v>206</v>
-      </c>
-      <c r="C53" t="s">
-        <v>214</v>
-      </c>
-      <c r="D53" s="6">
-        <v>45782.602534722224</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F53" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G53">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A54" t="s">
-        <v>54</v>
-      </c>
-      <c r="B54" t="s">
-        <v>206</v>
-      </c>
-      <c r="C54" t="s">
-        <v>216</v>
-      </c>
-      <c r="D54" s="6">
-        <v>45782.602534722224</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F54" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G54">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" t="s">
-        <v>206</v>
-      </c>
-      <c r="C55" t="s">
-        <v>216</v>
-      </c>
-      <c r="D55" s="6">
-        <v>45782.602534722224</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F55" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>116</v>
-      </c>
-      <c r="B56" t="s">
-        <v>214</v>
-      </c>
-      <c r="C56" t="s">
-        <v>211</v>
-      </c>
-      <c r="D56" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F56" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G56">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>443</v>
-      </c>
-      <c r="B57" t="s">
-        <v>214</v>
-      </c>
-      <c r="C57" t="s">
-        <v>211</v>
-      </c>
-      <c r="D57" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F57" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G57">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>205</v>
-      </c>
-      <c r="B58" t="s">
-        <v>214</v>
-      </c>
-      <c r="C58" t="s">
-        <v>217</v>
-      </c>
-      <c r="D58" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F58" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" t="s">
-        <v>214</v>
-      </c>
-      <c r="C59" t="s">
-        <v>217</v>
-      </c>
-      <c r="D59" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F59" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G59">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>178</v>
-      </c>
-      <c r="B60" t="s">
-        <v>214</v>
-      </c>
-      <c r="C60" t="s">
-        <v>211</v>
-      </c>
-      <c r="D60" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F60" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G60">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>12</v>
-      </c>
-      <c r="B61" t="s">
-        <v>214</v>
-      </c>
-      <c r="C61" t="s">
-        <v>211</v>
-      </c>
-      <c r="D61" s="6">
-        <v>45782.607708333337</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F61" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>115</v>
-      </c>
-      <c r="B62" t="s">
-        <v>214</v>
-      </c>
-      <c r="C62" t="s">
-        <v>217</v>
-      </c>
-      <c r="D62" s="6">
-        <v>45782.609733796293</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F62" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>165</v>
-      </c>
-      <c r="B63" t="s">
-        <v>214</v>
-      </c>
-      <c r="C63" t="s">
-        <v>217</v>
-      </c>
-      <c r="D63" s="6">
-        <v>45782.609733796293</v>
-      </c>
-      <c r="E63" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F63" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>160</v>
-      </c>
-      <c r="B64" t="s">
-        <v>214</v>
-      </c>
-      <c r="C64" t="s">
-        <v>217</v>
-      </c>
-      <c r="D64" s="6">
-        <v>45782.609733796293</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F64" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" t="s">
-        <v>214</v>
-      </c>
-      <c r="C65" t="s">
-        <v>217</v>
-      </c>
-      <c r="D65" s="6">
-        <v>45782.609733796293</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F65" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G65">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A66" t="s">
-        <v>156</v>
-      </c>
-      <c r="B66" t="s">
-        <v>213</v>
-      </c>
-      <c r="C66" t="s">
-        <v>211</v>
-      </c>
-      <c r="D66" s="6">
-        <v>45782.610798611109</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F66" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
-        <v>96</v>
-      </c>
-      <c r="B67" t="s">
-        <v>213</v>
-      </c>
-      <c r="C67" t="s">
-        <v>211</v>
-      </c>
-      <c r="D67" s="6">
-        <v>45782.610798611109</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F67" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>52</v>
-      </c>
-      <c r="B68" t="s">
-        <v>213</v>
-      </c>
-      <c r="C68" t="s">
-        <v>211</v>
-      </c>
-      <c r="D68" s="6">
-        <v>45782.610798611109</v>
-      </c>
-      <c r="E68" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F68" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G68">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>204</v>
-      </c>
-      <c r="B69" t="s">
-        <v>213</v>
-      </c>
-      <c r="C69" t="s">
-        <v>211</v>
-      </c>
-      <c r="D69" s="6">
-        <v>45782.610798611109</v>
-      </c>
-      <c r="E69" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F69" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G69">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>63</v>
-      </c>
-      <c r="B70" t="s">
-        <v>211</v>
-      </c>
-      <c r="C70" t="s">
-        <v>214</v>
-      </c>
-      <c r="D70" s="6">
-        <v>45782.61577546296</v>
-      </c>
-      <c r="E70" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F70" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>203</v>
-      </c>
-      <c r="B71" t="s">
-        <v>213</v>
-      </c>
-      <c r="C71" t="s">
-        <v>214</v>
-      </c>
-      <c r="D71" s="6">
-        <v>45782.617743055554</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F71" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G71">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>127</v>
-      </c>
-      <c r="B72" t="s">
-        <v>213</v>
-      </c>
-      <c r="C72" t="s">
-        <v>214</v>
-      </c>
-      <c r="D72" s="6">
-        <v>45782.617743055554</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F72" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G72">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>111</v>
-      </c>
-      <c r="B73" t="s">
-        <v>213</v>
-      </c>
-      <c r="C73" t="s">
-        <v>214</v>
-      </c>
-      <c r="D73" s="6">
-        <v>45782.617743055554</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F73" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G73">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A74" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" t="s">
-        <v>213</v>
-      </c>
-      <c r="C74" t="s">
-        <v>214</v>
-      </c>
-      <c r="D74" s="6">
-        <v>45782.61859953704</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F74" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G74">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>176</v>
-      </c>
-      <c r="B75" t="s">
-        <v>213</v>
-      </c>
-      <c r="C75" t="s">
-        <v>211</v>
-      </c>
-      <c r="D75" s="6">
-        <v>45782.61859953704</v>
-      </c>
-      <c r="E75" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F75" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>369</v>
-      </c>
-      <c r="B76" t="s">
-        <v>213</v>
-      </c>
-      <c r="C76" t="s">
-        <v>214</v>
-      </c>
-      <c r="D76" s="6">
-        <v>45782.61859953704</v>
-      </c>
-      <c r="E76" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F76" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>442</v>
-      </c>
-      <c r="B77" t="s">
-        <v>213</v>
-      </c>
-      <c r="C77" t="s">
-        <v>211</v>
-      </c>
-      <c r="D77" s="6">
-        <v>45782.61859953704</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F77" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" t="s">
-        <v>213</v>
-      </c>
-      <c r="C78" t="s">
-        <v>211</v>
-      </c>
-      <c r="D78" s="6">
-        <v>45782.61859953704</v>
-      </c>
-      <c r="E78" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F78" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G78">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A79" t="s">
-        <v>124</v>
-      </c>
-      <c r="B79" t="s">
-        <v>211</v>
-      </c>
-      <c r="C79" t="s">
-        <v>214</v>
-      </c>
-      <c r="D79" s="6">
-        <v>45782.618634259263</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F79" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G79">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A80" t="s">
-        <v>56</v>
-      </c>
-      <c r="B80" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s">
-        <v>214</v>
-      </c>
-      <c r="D80" s="6">
-        <v>45782.618634259263</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F80" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G80">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A81" t="s">
-        <v>40</v>
-      </c>
-      <c r="B81" t="s">
-        <v>211</v>
-      </c>
-      <c r="C81" t="s">
-        <v>214</v>
-      </c>
-      <c r="D81" s="6">
-        <v>45782.618634259263</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F81" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A82" t="s">
-        <v>44</v>
-      </c>
-      <c r="B82" t="s">
-        <v>211</v>
-      </c>
-      <c r="C82" t="s">
-        <v>214</v>
-      </c>
-      <c r="D82" s="6">
-        <v>45782.618634259263</v>
-      </c>
-      <c r="E82" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F82" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G82">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>140</v>
-      </c>
-      <c r="B83" t="s">
-        <v>211</v>
-      </c>
-      <c r="C83" t="s">
-        <v>214</v>
-      </c>
-      <c r="D83" s="6">
-        <v>45782.618634259263</v>
-      </c>
-      <c r="E83" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F83" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G83">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>104</v>
-      </c>
-      <c r="B84" t="s">
-        <v>210</v>
-      </c>
-      <c r="C84" t="s">
-        <v>214</v>
-      </c>
-      <c r="D84" s="6">
-        <v>45782.624467592592</v>
-      </c>
-      <c r="E84" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F84" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G84">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>134</v>
-      </c>
-      <c r="B85" t="s">
-        <v>210</v>
-      </c>
-      <c r="C85" t="s">
-        <v>211</v>
-      </c>
-      <c r="D85" s="6">
-        <v>45782.624467592592</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F85" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G85">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>185</v>
-      </c>
-      <c r="B86" t="s">
-        <v>210</v>
-      </c>
-      <c r="C86" t="s">
-        <v>214</v>
-      </c>
-      <c r="D86" s="6">
-        <v>45782.624467592592</v>
-      </c>
-      <c r="E86" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F86" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>194</v>
-      </c>
-      <c r="B87" t="s">
-        <v>210</v>
-      </c>
-      <c r="C87" t="s">
-        <v>211</v>
-      </c>
-      <c r="D87" s="6">
-        <v>45782.624467592592</v>
-      </c>
-      <c r="E87" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F87" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" t="s">
-        <v>210</v>
-      </c>
-      <c r="C88" t="s">
-        <v>214</v>
-      </c>
-      <c r="D88" s="6">
-        <v>45782.624467592592</v>
-      </c>
-      <c r="E88" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F88" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>174</v>
-      </c>
-      <c r="B89" t="s">
-        <v>214</v>
-      </c>
-      <c r="C89" t="s">
-        <v>211</v>
-      </c>
-      <c r="D89" s="6">
-        <v>45782.649363425924</v>
-      </c>
-      <c r="E89" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F89" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G89">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>88</v>
-      </c>
-      <c r="B90" t="s">
-        <v>220</v>
-      </c>
-      <c r="C90" t="s">
-        <v>211</v>
-      </c>
-      <c r="D90" s="6">
-        <v>45782.661354166667</v>
-      </c>
-      <c r="E90" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F90" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G90">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>47</v>
-      </c>
-      <c r="B91" t="s">
-        <v>213</v>
-      </c>
-      <c r="C91" t="s">
-        <v>214</v>
-      </c>
-      <c r="D91" s="6">
-        <v>45782.675000000003</v>
-      </c>
-      <c r="E91" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F91" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G91">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A92" t="s">
-        <v>70</v>
-      </c>
-      <c r="B92" t="s">
-        <v>213</v>
-      </c>
-      <c r="C92" t="s">
-        <v>214</v>
-      </c>
-      <c r="D92" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E92" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F92" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G92">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A93" t="s">
-        <v>128</v>
-      </c>
-      <c r="B93" t="s">
-        <v>213</v>
-      </c>
-      <c r="C93" t="s">
-        <v>214</v>
-      </c>
-      <c r="D93" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F93" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G93">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A94" t="s">
-        <v>49</v>
-      </c>
-      <c r="B94" t="s">
-        <v>213</v>
-      </c>
-      <c r="C94" t="s">
-        <v>214</v>
-      </c>
-      <c r="D94" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F94" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G94">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A95" t="s">
-        <v>74</v>
-      </c>
-      <c r="B95" t="s">
-        <v>213</v>
-      </c>
-      <c r="C95" t="s">
-        <v>214</v>
-      </c>
-      <c r="D95" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E95" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F95" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G95">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>408</v>
-      </c>
-      <c r="B96" t="s">
-        <v>213</v>
-      </c>
-      <c r="C96" t="s">
-        <v>216</v>
-      </c>
-      <c r="D96" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E96" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F96" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>410</v>
-      </c>
-      <c r="B97" t="s">
-        <v>213</v>
-      </c>
-      <c r="C97" t="s">
-        <v>216</v>
-      </c>
-      <c r="D97" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E97" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F97" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>412</v>
-      </c>
-      <c r="B98" t="s">
-        <v>213</v>
-      </c>
-      <c r="C98" t="s">
-        <v>216</v>
-      </c>
-      <c r="D98" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E98" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F98" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G98">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>414</v>
-      </c>
-      <c r="B99" t="s">
-        <v>213</v>
-      </c>
-      <c r="C99" t="s">
-        <v>216</v>
-      </c>
-      <c r="D99" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E99" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F99" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G99">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A100" t="s">
-        <v>416</v>
-      </c>
-      <c r="B100" t="s">
-        <v>213</v>
-      </c>
-      <c r="C100" t="s">
-        <v>216</v>
-      </c>
-      <c r="D100" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E100" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F100" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G100">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>418</v>
-      </c>
-      <c r="B101" t="s">
-        <v>213</v>
-      </c>
-      <c r="C101" t="s">
-        <v>216</v>
-      </c>
-      <c r="D101" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F101" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G101">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>453</v>
-      </c>
-      <c r="B102" t="s">
-        <v>213</v>
-      </c>
-      <c r="C102" t="s">
-        <v>216</v>
-      </c>
-      <c r="D102" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E102" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F102" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G102">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>455</v>
-      </c>
-      <c r="B103" t="s">
-        <v>213</v>
-      </c>
-      <c r="C103" t="s">
-        <v>216</v>
-      </c>
-      <c r="D103" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E103" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F103" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G103">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>476</v>
-      </c>
-      <c r="B104" t="s">
-        <v>213</v>
-      </c>
-      <c r="C104" t="s">
-        <v>214</v>
-      </c>
-      <c r="D104" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E104" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F104" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A105" t="s">
-        <v>477</v>
-      </c>
-      <c r="B105" t="s">
-        <v>213</v>
-      </c>
-      <c r="C105" t="s">
-        <v>216</v>
-      </c>
-      <c r="D105" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E105" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F105" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G105">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A106" t="s">
-        <v>481</v>
-      </c>
-      <c r="B106" t="s">
-        <v>213</v>
-      </c>
-      <c r="C106" t="s">
-        <v>214</v>
-      </c>
-      <c r="D106" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E106" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F106" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G106">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A107" t="s">
-        <v>482</v>
-      </c>
-      <c r="B107" t="s">
-        <v>213</v>
-      </c>
-      <c r="C107" t="s">
-        <v>214</v>
-      </c>
-      <c r="D107" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E107" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F107" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G107">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A108" t="s">
-        <v>75</v>
-      </c>
-      <c r="B108" t="s">
-        <v>213</v>
-      </c>
-      <c r="C108" t="s">
-        <v>214</v>
-      </c>
-      <c r="D108" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E108" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F108" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G108">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>141</v>
-      </c>
-      <c r="B109" t="s">
-        <v>213</v>
-      </c>
-      <c r="C109" t="s">
-        <v>214</v>
-      </c>
-      <c r="D109" s="6">
-        <v>45782.676215277781</v>
-      </c>
-      <c r="E109" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F109" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G109">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>102</v>
-      </c>
-      <c r="B110" t="s">
-        <v>214</v>
-      </c>
-      <c r="C110" t="s">
-        <v>216</v>
-      </c>
-      <c r="D110" s="6">
-        <v>45782.691886574074</v>
-      </c>
-      <c r="E110" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F110" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>136</v>
-      </c>
-      <c r="B111" t="s">
-        <v>214</v>
-      </c>
-      <c r="C111" t="s">
-        <v>211</v>
-      </c>
-      <c r="D111" s="6">
-        <v>45782.691886574074</v>
-      </c>
-      <c r="E111" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F111" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G111">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>444</v>
-      </c>
-      <c r="B112" t="s">
-        <v>214</v>
-      </c>
-      <c r="C112" t="s">
-        <v>211</v>
-      </c>
-      <c r="D112" s="6">
-        <v>45782.701504629629</v>
-      </c>
-      <c r="E112" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F112" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G112">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A113" t="s">
-        <v>181</v>
-      </c>
-      <c r="B113" t="s">
-        <v>214</v>
-      </c>
-      <c r="C113" t="s">
-        <v>211</v>
-      </c>
-      <c r="D113" s="6">
-        <v>45782.701504629629</v>
-      </c>
-      <c r="E113" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F113" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G113">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>146</v>
-      </c>
-      <c r="B114" t="s">
-        <v>214</v>
-      </c>
-      <c r="C114" t="s">
-        <v>216</v>
-      </c>
-      <c r="D114" s="6">
-        <v>45782.733946759261</v>
-      </c>
-      <c r="E114" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F114" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G114">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>152</v>
-      </c>
-      <c r="B115" t="s">
-        <v>214</v>
-      </c>
-      <c r="C115" t="s">
-        <v>216</v>
-      </c>
-      <c r="D115" s="6">
-        <v>45782.733946759261</v>
-      </c>
-      <c r="E115" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F115" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>107</v>
-      </c>
-      <c r="B116" t="s">
-        <v>214</v>
-      </c>
-      <c r="C116" t="s">
-        <v>216</v>
-      </c>
-      <c r="D116" s="6">
-        <v>45782.733946759261</v>
-      </c>
-      <c r="E116" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F116" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G116">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>89</v>
-      </c>
-      <c r="B117" t="s">
-        <v>220</v>
-      </c>
-      <c r="C117" t="s">
-        <v>211</v>
-      </c>
-      <c r="D117" s="6">
-        <v>45782.736539351848</v>
-      </c>
-      <c r="E117" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F117" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G117">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A118" t="s">
-        <v>197</v>
-      </c>
-      <c r="B118" t="s">
-        <v>214</v>
-      </c>
-      <c r="C118" t="s">
-        <v>211</v>
-      </c>
-      <c r="D118" s="6">
-        <v>45782.787604166668</v>
-      </c>
-      <c r="E118" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F118" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G118">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A119" t="s">
-        <v>99</v>
-      </c>
-      <c r="B119" t="s">
-        <v>214</v>
-      </c>
-      <c r="C119" t="s">
-        <v>211</v>
-      </c>
-      <c r="D119" s="6">
-        <v>45782.787604166668</v>
-      </c>
-      <c r="E119" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F119" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G119">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A120" t="s">
-        <v>90</v>
-      </c>
-      <c r="B120" t="s">
-        <v>220</v>
-      </c>
-      <c r="C120" t="s">
-        <v>211</v>
-      </c>
-      <c r="D120" s="6">
-        <v>45782.80027777778</v>
-      </c>
-      <c r="E120" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F120" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G120">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A121" t="s">
-        <v>432</v>
-      </c>
-      <c r="B121" t="s">
-        <v>211</v>
-      </c>
-      <c r="C121" t="s">
-        <v>213</v>
-      </c>
-      <c r="D121" s="6">
-        <v>45782.808287037034</v>
-      </c>
-      <c r="E121" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F121" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G121">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A122" t="s">
-        <v>374</v>
-      </c>
-      <c r="B122" t="s">
-        <v>214</v>
-      </c>
-      <c r="C122" t="s">
-        <v>211</v>
-      </c>
-      <c r="D122" s="6">
-        <v>45782.811215277776</v>
-      </c>
-      <c r="E122" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F122" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G122">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>373</v>
-      </c>
-      <c r="B123" t="s">
-        <v>214</v>
-      </c>
-      <c r="C123" t="s">
-        <v>211</v>
-      </c>
-      <c r="D123" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E123" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F123" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G123">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" t="s">
-        <v>375</v>
-      </c>
-      <c r="B124" t="s">
-        <v>214</v>
-      </c>
-      <c r="C124" t="s">
-        <v>211</v>
-      </c>
-      <c r="D124" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E124" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F124" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G124">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" t="s">
-        <v>380</v>
-      </c>
-      <c r="B125" t="s">
-        <v>214</v>
-      </c>
-      <c r="C125" t="s">
-        <v>211</v>
-      </c>
-      <c r="D125" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E125" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F125" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G125">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>381</v>
-      </c>
-      <c r="B126" t="s">
-        <v>214</v>
-      </c>
-      <c r="C126" t="s">
-        <v>211</v>
-      </c>
-      <c r="D126" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E126" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F126" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G126">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" t="s">
-        <v>436</v>
-      </c>
-      <c r="B127" t="s">
-        <v>214</v>
-      </c>
-      <c r="C127" t="s">
-        <v>211</v>
-      </c>
-      <c r="D127" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E127" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F127" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G127">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" t="s">
-        <v>437</v>
-      </c>
-      <c r="B128" t="s">
-        <v>214</v>
-      </c>
-      <c r="C128" t="s">
-        <v>211</v>
-      </c>
-      <c r="D128" s="6">
-        <v>45782.811226851853</v>
-      </c>
-      <c r="E128" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F128" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" t="s">
-        <v>486</v>
-      </c>
-      <c r="B129" t="s">
-        <v>214</v>
-      </c>
-      <c r="C129" t="s">
-        <v>216</v>
-      </c>
-      <c r="D129" s="6">
-        <v>45782.818182870367</v>
-      </c>
-      <c r="E129" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F129" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G129">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" t="s">
-        <v>485</v>
-      </c>
-      <c r="B130" t="s">
-        <v>211</v>
-      </c>
-      <c r="C130" t="s">
-        <v>216</v>
-      </c>
-      <c r="D130" s="6">
-        <v>45782.830289351848</v>
-      </c>
-      <c r="E130" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F130" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G130">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" t="s">
-        <v>7</v>
-      </c>
-      <c r="B131" t="s">
-        <v>211</v>
-      </c>
-      <c r="C131" t="s">
-        <v>214</v>
-      </c>
-      <c r="D131" s="6">
-        <v>45782.830289351848</v>
-      </c>
-      <c r="E131" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F131" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G131">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" t="s">
-        <v>25</v>
-      </c>
-      <c r="B132" t="s">
-        <v>211</v>
-      </c>
-      <c r="C132" t="s">
-        <v>216</v>
-      </c>
-      <c r="D132" s="6">
-        <v>45782.841412037036</v>
-      </c>
-      <c r="E132" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F132" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G132">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" t="s">
-        <v>191</v>
-      </c>
-      <c r="B133" t="s">
-        <v>211</v>
-      </c>
-      <c r="C133" t="s">
-        <v>216</v>
-      </c>
-      <c r="D133" s="6">
-        <v>45782.841886574075</v>
-      </c>
-      <c r="E133" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F133" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G133">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A134" t="s">
-        <v>472</v>
-      </c>
-      <c r="B134" t="s">
-        <v>214</v>
-      </c>
-      <c r="C134" t="s">
-        <v>213</v>
-      </c>
-      <c r="D134" s="6">
-        <v>45782.842523148145</v>
-      </c>
-      <c r="E134" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F134" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G134">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A135" t="s">
-        <v>473</v>
-      </c>
-      <c r="B135" t="s">
-        <v>214</v>
-      </c>
-      <c r="C135" t="s">
-        <v>213</v>
-      </c>
-      <c r="D135" s="6">
-        <v>45782.842523148145</v>
-      </c>
-      <c r="E135" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F135" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G135">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A136" t="s">
-        <v>474</v>
-      </c>
-      <c r="B136" t="s">
-        <v>214</v>
-      </c>
-      <c r="C136" t="s">
-        <v>213</v>
-      </c>
-      <c r="D136" s="6">
-        <v>45782.842523148145</v>
-      </c>
-      <c r="E136" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F136" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G136">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A137" t="s">
-        <v>475</v>
-      </c>
-      <c r="B137" t="s">
-        <v>214</v>
-      </c>
-      <c r="C137" t="s">
-        <v>213</v>
-      </c>
-      <c r="D137" s="6">
-        <v>45782.842523148145</v>
-      </c>
-      <c r="E137" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F137" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G137">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A138" t="s">
-        <v>169</v>
-      </c>
-      <c r="B138" t="s">
-        <v>219</v>
-      </c>
-      <c r="C138" t="s">
-        <v>213</v>
-      </c>
-      <c r="D138" s="6">
-        <v>45782.843009259261</v>
-      </c>
-      <c r="E138" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F138" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G138">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A139" t="s">
-        <v>60</v>
-      </c>
-      <c r="B139" t="s">
-        <v>211</v>
-      </c>
-      <c r="C139" t="s">
-        <v>214</v>
-      </c>
-      <c r="D139" s="6">
-        <v>45782.8440162037</v>
-      </c>
-      <c r="E139" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F139" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G139">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>396</v>
-      </c>
-      <c r="B140" t="s">
-        <v>211</v>
-      </c>
-      <c r="C140" t="s">
-        <v>216</v>
-      </c>
-      <c r="D140" s="6">
-        <v>45782.844027777777</v>
-      </c>
-      <c r="E140" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F140" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G140">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A141" t="s">
-        <v>397</v>
-      </c>
-      <c r="B141" t="s">
-        <v>211</v>
-      </c>
-      <c r="C141" t="s">
-        <v>216</v>
-      </c>
-      <c r="D141" s="6">
-        <v>45782.844027777777</v>
-      </c>
-      <c r="E141" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F141" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G141">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A142" t="s">
-        <v>73</v>
-      </c>
-      <c r="B142" t="s">
-        <v>211</v>
-      </c>
-      <c r="C142" t="s">
-        <v>216</v>
-      </c>
-      <c r="D142" s="6">
-        <v>45782.847511574073</v>
-      </c>
-      <c r="E142" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F142" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G142">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A143" t="s">
-        <v>420</v>
-      </c>
-      <c r="B143" t="s">
-        <v>211</v>
-      </c>
-      <c r="C143" t="s">
-        <v>216</v>
-      </c>
-      <c r="D143" s="6">
-        <v>45782.855613425927</v>
-      </c>
-      <c r="E143" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F143" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G143">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A144" t="s">
-        <v>421</v>
-      </c>
-      <c r="B144" t="s">
-        <v>211</v>
-      </c>
-      <c r="C144" t="s">
-        <v>216</v>
-      </c>
-      <c r="D144" s="6">
-        <v>45782.855613425927</v>
-      </c>
-      <c r="E144" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F144" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G144">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A145" t="s">
-        <v>422</v>
-      </c>
-      <c r="B145" t="s">
-        <v>211</v>
-      </c>
-      <c r="C145" t="s">
-        <v>216</v>
-      </c>
-      <c r="D145" s="6">
-        <v>45782.855613425927</v>
-      </c>
-      <c r="E145" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F145" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G145">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A146" t="s">
-        <v>423</v>
-      </c>
-      <c r="B146" t="s">
-        <v>211</v>
-      </c>
-      <c r="C146" t="s">
-        <v>216</v>
-      </c>
-      <c r="D146" s="6">
-        <v>45782.855613425927</v>
-      </c>
-      <c r="E146" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F146" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G146">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A147" t="s">
-        <v>424</v>
-      </c>
-      <c r="B147" t="s">
-        <v>211</v>
-      </c>
-      <c r="C147" t="s">
-        <v>216</v>
-      </c>
-      <c r="D147" s="6">
-        <v>45782.855613425927</v>
-      </c>
-      <c r="E147" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F147" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G147">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A148" t="s">
-        <v>157</v>
-      </c>
-      <c r="B148" t="s">
-        <v>211</v>
-      </c>
-      <c r="C148" t="s">
-        <v>216</v>
-      </c>
-      <c r="D148" s="6">
-        <v>45782.857997685183</v>
-      </c>
-      <c r="E148" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F148" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G148">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A149" t="s">
-        <v>361</v>
-      </c>
-      <c r="B149" t="s">
-        <v>211</v>
-      </c>
-      <c r="C149" t="s">
-        <v>214</v>
-      </c>
-      <c r="D149" s="6">
-        <v>45782.857997685183</v>
-      </c>
-      <c r="E149" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F149" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G149">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A150" t="s">
-        <v>22</v>
-      </c>
-      <c r="B150" t="s">
-        <v>211</v>
-      </c>
-      <c r="C150" t="s">
-        <v>216</v>
-      </c>
-      <c r="D150" s="6">
-        <v>45782.857997685183</v>
-      </c>
-      <c r="E150" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F150" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G150">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A151" t="s">
-        <v>11</v>
-      </c>
-      <c r="B151" t="s">
-        <v>211</v>
-      </c>
-      <c r="C151" t="s">
-        <v>214</v>
-      </c>
-      <c r="D151" s="6">
-        <v>45782.860474537039</v>
-      </c>
-      <c r="E151" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F151" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G151">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A152" t="s">
-        <v>6</v>
-      </c>
-      <c r="B152" t="s">
-        <v>211</v>
-      </c>
-      <c r="C152" t="s">
-        <v>214</v>
-      </c>
-      <c r="D152" s="6">
-        <v>45782.860474537039</v>
-      </c>
-      <c r="E152" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F152" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G152">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A153" t="s">
-        <v>179</v>
-      </c>
-      <c r="B153" t="s">
-        <v>211</v>
-      </c>
-      <c r="C153" t="s">
-        <v>214</v>
-      </c>
-      <c r="D153" s="6">
-        <v>45782.860474537039</v>
-      </c>
-      <c r="E153" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F153" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G153">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A154" t="s">
-        <v>153</v>
-      </c>
-      <c r="B154" t="s">
-        <v>211</v>
-      </c>
-      <c r="C154" t="s">
-        <v>216</v>
-      </c>
-      <c r="D154" s="6">
-        <v>45782.860474537039</v>
-      </c>
-      <c r="E154" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F154" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G154">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" t="s">
-        <v>126</v>
-      </c>
-      <c r="B155" t="s">
-        <v>211</v>
-      </c>
-      <c r="C155" t="s">
-        <v>214</v>
-      </c>
-      <c r="D155" s="6">
-        <v>45782.886053240742</v>
-      </c>
-      <c r="E155" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F155" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G155">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" t="s">
-        <v>434</v>
-      </c>
-      <c r="B156" t="s">
-        <v>211</v>
-      </c>
-      <c r="C156" t="s">
-        <v>213</v>
-      </c>
-      <c r="D156" s="6">
-        <v>45782.889710648145</v>
-      </c>
-      <c r="E156" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F156" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G156">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" t="s">
-        <v>138</v>
-      </c>
-      <c r="B157" t="s">
-        <v>214</v>
-      </c>
-      <c r="C157" t="s">
-        <v>211</v>
-      </c>
-      <c r="D157" s="6">
-        <v>45782.8903587963</v>
-      </c>
-      <c r="E157" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F157" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G157">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A158" t="s">
-        <v>170</v>
-      </c>
-      <c r="B158" t="s">
-        <v>214</v>
-      </c>
-      <c r="C158" t="s">
-        <v>216</v>
-      </c>
-      <c r="D158" s="6">
-        <v>45782.8903587963</v>
-      </c>
-      <c r="E158" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F158" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G158">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A159" t="s">
-        <v>46</v>
-      </c>
-      <c r="B159" t="s">
-        <v>213</v>
-      </c>
-      <c r="C159" t="s">
-        <v>214</v>
-      </c>
-      <c r="D159" s="6">
-        <v>45782.896782407406</v>
-      </c>
-      <c r="E159" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F159" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G159">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A160" t="s">
-        <v>186</v>
-      </c>
-      <c r="B160" t="s">
-        <v>211</v>
-      </c>
-      <c r="C160" t="s">
-        <v>216</v>
-      </c>
-      <c r="D160" s="6">
-        <v>45782.897245370368</v>
-      </c>
-      <c r="E160" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F160" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G160">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A161" t="s">
-        <v>449</v>
-      </c>
-      <c r="B161" t="s">
-        <v>214</v>
-      </c>
-      <c r="C161" t="s">
-        <v>216</v>
-      </c>
-      <c r="D161" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E161" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F161" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G161">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A162" t="s">
-        <v>450</v>
-      </c>
-      <c r="B162" t="s">
-        <v>214</v>
-      </c>
-      <c r="C162" t="s">
-        <v>216</v>
-      </c>
-      <c r="D162" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E162" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F162" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G162">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A163" t="s">
-        <v>464</v>
-      </c>
-      <c r="B163" t="s">
-        <v>214</v>
-      </c>
-      <c r="C163" t="s">
-        <v>216</v>
-      </c>
-      <c r="D163" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E163" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F163" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G163">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A164" t="s">
-        <v>465</v>
-      </c>
-      <c r="B164" t="s">
-        <v>214</v>
-      </c>
-      <c r="C164" t="s">
-        <v>216</v>
-      </c>
-      <c r="D164" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E164" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F164" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G164">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A165" t="s">
-        <v>466</v>
-      </c>
-      <c r="B165" t="s">
-        <v>214</v>
-      </c>
-      <c r="C165" t="s">
-        <v>216</v>
-      </c>
-      <c r="D165" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E165" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F165" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G165">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A166" t="s">
-        <v>467</v>
-      </c>
-      <c r="B166" t="s">
-        <v>214</v>
-      </c>
-      <c r="C166" t="s">
-        <v>216</v>
-      </c>
-      <c r="D166" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E166" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F166" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G166">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A167" t="s">
-        <v>471</v>
-      </c>
-      <c r="B167" t="s">
-        <v>214</v>
-      </c>
-      <c r="C167" t="s">
-        <v>216</v>
-      </c>
-      <c r="D167" s="6">
-        <v>45782.897800925923</v>
-      </c>
-      <c r="E167" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F167" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G167">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A168" t="s">
-        <v>446</v>
-      </c>
-      <c r="B168" t="s">
-        <v>214</v>
-      </c>
-      <c r="C168" t="s">
-        <v>216</v>
-      </c>
-      <c r="D168" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E168" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F168" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G168">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A169" t="s">
-        <v>447</v>
-      </c>
-      <c r="B169" t="s">
-        <v>214</v>
-      </c>
-      <c r="C169" t="s">
-        <v>216</v>
-      </c>
-      <c r="D169" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E169" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F169" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G169">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A170" t="s">
-        <v>448</v>
-      </c>
-      <c r="B170" t="s">
-        <v>214</v>
-      </c>
-      <c r="C170" t="s">
-        <v>216</v>
-      </c>
-      <c r="D170" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E170" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F170" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G170">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A171" t="s">
-        <v>451</v>
-      </c>
-      <c r="B171" t="s">
-        <v>214</v>
-      </c>
-      <c r="C171" t="s">
-        <v>216</v>
-      </c>
-      <c r="D171" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E171" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F171" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G171">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A172" t="s">
-        <v>452</v>
-      </c>
-      <c r="B172" t="s">
-        <v>214</v>
-      </c>
-      <c r="C172" t="s">
-        <v>216</v>
-      </c>
-      <c r="D172" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E172" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F172" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G172">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A173" t="s">
-        <v>463</v>
-      </c>
-      <c r="B173" t="s">
-        <v>214</v>
-      </c>
-      <c r="C173" t="s">
-        <v>216</v>
-      </c>
-      <c r="D173" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E173" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F173" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G173">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A174" t="s">
-        <v>468</v>
-      </c>
-      <c r="B174" t="s">
-        <v>214</v>
-      </c>
-      <c r="C174" t="s">
-        <v>216</v>
-      </c>
-      <c r="D174" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E174" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F174" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G174">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A175" t="s">
-        <v>469</v>
-      </c>
-      <c r="B175" t="s">
-        <v>214</v>
-      </c>
-      <c r="C175" t="s">
-        <v>216</v>
-      </c>
-      <c r="D175" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E175" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F175" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G175">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A176" t="s">
-        <v>470</v>
-      </c>
-      <c r="B176" t="s">
-        <v>214</v>
-      </c>
-      <c r="C176" t="s">
-        <v>216</v>
-      </c>
-      <c r="D176" s="6">
-        <v>45782.897812499999</v>
-      </c>
-      <c r="E176" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F176" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G176">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A177" t="s">
-        <v>183</v>
-      </c>
-      <c r="B177" t="s">
-        <v>214</v>
-      </c>
-      <c r="C177" t="s">
-        <v>211</v>
-      </c>
-      <c r="D177" s="6">
-        <v>45782.905127314814</v>
-      </c>
-      <c r="E177" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F177" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G177">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A178" t="s">
-        <v>64</v>
-      </c>
-      <c r="B178" t="s">
-        <v>214</v>
-      </c>
-      <c r="C178" t="s">
-        <v>211</v>
-      </c>
-      <c r="D178" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E178" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F178" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G178">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A179" t="s">
-        <v>18</v>
-      </c>
-      <c r="B179" t="s">
-        <v>214</v>
-      </c>
-      <c r="C179" t="s">
-        <v>211</v>
-      </c>
-      <c r="D179" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E179" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F179" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G179">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A180" t="s">
-        <v>41</v>
-      </c>
-      <c r="B180" t="s">
-        <v>214</v>
-      </c>
-      <c r="C180" t="s">
-        <v>211</v>
-      </c>
-      <c r="D180" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E180" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F180" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G180">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A181" t="s">
-        <v>37</v>
-      </c>
-      <c r="B181" t="s">
-        <v>214</v>
-      </c>
-      <c r="C181" t="s">
-        <v>211</v>
-      </c>
-      <c r="D181" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E181" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F181" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G181">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A182" t="s">
-        <v>188</v>
-      </c>
-      <c r="B182" t="s">
-        <v>214</v>
-      </c>
-      <c r="C182" t="s">
-        <v>211</v>
-      </c>
-      <c r="D182" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E182" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F182" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G182">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A183" t="s">
-        <v>150</v>
-      </c>
-      <c r="B183" t="s">
-        <v>214</v>
-      </c>
-      <c r="C183" t="s">
-        <v>211</v>
-      </c>
-      <c r="D183" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E183" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F183" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G183">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A184" t="s">
-        <v>9</v>
-      </c>
-      <c r="B184" t="s">
-        <v>214</v>
-      </c>
-      <c r="C184" t="s">
-        <v>211</v>
-      </c>
-      <c r="D184" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E184" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F184" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G184">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A185" t="s">
-        <v>80</v>
-      </c>
-      <c r="B185" t="s">
-        <v>214</v>
-      </c>
-      <c r="C185" t="s">
-        <v>211</v>
-      </c>
-      <c r="D185" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E185" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F185" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G185">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A186" t="s">
-        <v>192</v>
-      </c>
-      <c r="B186" t="s">
-        <v>214</v>
-      </c>
-      <c r="C186" t="s">
-        <v>211</v>
-      </c>
-      <c r="D186" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E186" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F186" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G186">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A187" t="s">
-        <v>91</v>
-      </c>
-      <c r="B187" t="s">
-        <v>214</v>
-      </c>
-      <c r="C187" t="s">
-        <v>211</v>
-      </c>
-      <c r="D187" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E187" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F187" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G187">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A188" t="s">
-        <v>65</v>
-      </c>
-      <c r="B188" t="s">
-        <v>214</v>
-      </c>
-      <c r="C188" t="s">
-        <v>211</v>
-      </c>
-      <c r="D188" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E188" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F188" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G188">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A189" t="s">
-        <v>168</v>
-      </c>
-      <c r="B189" t="s">
-        <v>214</v>
-      </c>
-      <c r="C189" t="s">
-        <v>211</v>
-      </c>
-      <c r="D189" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E189" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F189" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G189">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A190" t="s">
-        <v>61</v>
-      </c>
-      <c r="B190" t="s">
-        <v>214</v>
-      </c>
-      <c r="C190" t="s">
-        <v>211</v>
-      </c>
-      <c r="D190" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E190" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F190" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G190">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A191" t="s">
-        <v>66</v>
-      </c>
-      <c r="B191" t="s">
-        <v>214</v>
-      </c>
-      <c r="C191" t="s">
-        <v>211</v>
-      </c>
-      <c r="D191" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E191" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F191" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A192" t="s">
-        <v>34</v>
-      </c>
-      <c r="B192" t="s">
-        <v>214</v>
-      </c>
-      <c r="C192" t="s">
-        <v>211</v>
-      </c>
-      <c r="D192" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E192" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F192" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A193" t="s">
-        <v>86</v>
-      </c>
-      <c r="B193" t="s">
-        <v>214</v>
-      </c>
-      <c r="C193" t="s">
-        <v>211</v>
-      </c>
-      <c r="D193" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E193" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F193" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G193">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A194" t="s">
-        <v>172</v>
-      </c>
-      <c r="B194" t="s">
-        <v>214</v>
-      </c>
-      <c r="C194" t="s">
-        <v>211</v>
-      </c>
-      <c r="D194" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E194" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F194" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G194">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A195" t="s">
-        <v>376</v>
-      </c>
-      <c r="B195" t="s">
-        <v>214</v>
-      </c>
-      <c r="C195" t="s">
-        <v>211</v>
-      </c>
-      <c r="D195" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E195" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F195" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G195">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A196" t="s">
-        <v>377</v>
-      </c>
-      <c r="B196" t="s">
-        <v>214</v>
-      </c>
-      <c r="C196" t="s">
-        <v>211</v>
-      </c>
-      <c r="D196" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E196" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F196" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G196">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A197" t="s">
-        <v>378</v>
-      </c>
-      <c r="B197" t="s">
-        <v>214</v>
-      </c>
-      <c r="C197" t="s">
-        <v>211</v>
-      </c>
-      <c r="D197" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E197" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F197" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G197">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A198" t="s">
-        <v>379</v>
-      </c>
-      <c r="B198" t="s">
-        <v>214</v>
-      </c>
-      <c r="C198" t="s">
-        <v>211</v>
-      </c>
-      <c r="D198" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E198" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F198" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G198">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A199" t="s">
-        <v>382</v>
-      </c>
-      <c r="B199" t="s">
-        <v>214</v>
-      </c>
-      <c r="C199" t="s">
-        <v>211</v>
-      </c>
-      <c r="D199" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E199" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F199" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G199">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A200" t="s">
-        <v>384</v>
-      </c>
-      <c r="B200" t="s">
-        <v>214</v>
-      </c>
-      <c r="C200" t="s">
-        <v>211</v>
-      </c>
-      <c r="D200" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E200" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F200" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G200">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
-        <v>385</v>
-      </c>
-      <c r="B201" t="s">
-        <v>214</v>
-      </c>
-      <c r="C201" t="s">
-        <v>211</v>
-      </c>
-      <c r="D201" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E201" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F201" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G201">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A202" t="s">
-        <v>386</v>
-      </c>
-      <c r="B202" t="s">
-        <v>214</v>
-      </c>
-      <c r="C202" t="s">
-        <v>211</v>
-      </c>
-      <c r="D202" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E202" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F202" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G202">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A203" t="s">
-        <v>387</v>
-      </c>
-      <c r="B203" t="s">
-        <v>214</v>
-      </c>
-      <c r="C203" t="s">
-        <v>211</v>
-      </c>
-      <c r="D203" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E203" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F203" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G203">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A204" t="s">
-        <v>438</v>
-      </c>
-      <c r="B204" t="s">
-        <v>214</v>
-      </c>
-      <c r="C204" t="s">
-        <v>211</v>
-      </c>
-      <c r="D204" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E204" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F204" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G204">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A205" t="s">
-        <v>439</v>
-      </c>
-      <c r="B205" t="s">
-        <v>214</v>
-      </c>
-      <c r="C205" t="s">
-        <v>211</v>
-      </c>
-      <c r="D205" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E205" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F205" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G205">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A206" t="s">
-        <v>440</v>
-      </c>
-      <c r="B206" t="s">
-        <v>214</v>
-      </c>
-      <c r="C206" t="s">
-        <v>211</v>
-      </c>
-      <c r="D206" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E206" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F206" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G206">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A207" t="s">
-        <v>441</v>
-      </c>
-      <c r="B207" t="s">
-        <v>214</v>
-      </c>
-      <c r="C207" t="s">
-        <v>211</v>
-      </c>
-      <c r="D207" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E207" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F207" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G207">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A208" t="s">
-        <v>137</v>
-      </c>
-      <c r="B208" t="s">
-        <v>214</v>
-      </c>
-      <c r="C208" t="s">
-        <v>211</v>
-      </c>
-      <c r="D208" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E208" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F208" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G208">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
-        <v>13</v>
-      </c>
-      <c r="B209" t="s">
-        <v>214</v>
-      </c>
-      <c r="C209" t="s">
-        <v>211</v>
-      </c>
-      <c r="D209" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E209" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F209" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G209">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
-        <v>76</v>
-      </c>
-      <c r="B210" t="s">
-        <v>214</v>
-      </c>
-      <c r="C210" t="s">
-        <v>211</v>
-      </c>
-      <c r="D210" s="6">
-        <v>45782.905138888891</v>
-      </c>
-      <c r="E210" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F210" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G210">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
-        <v>58</v>
-      </c>
-      <c r="B211" t="s">
-        <v>211</v>
-      </c>
-      <c r="C211" t="s">
-        <v>216</v>
-      </c>
-      <c r="D211" s="6">
-        <v>45782.913298611114</v>
-      </c>
-      <c r="E211" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F211" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G211">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
-        <v>31</v>
-      </c>
-      <c r="B212" t="s">
-        <v>219</v>
-      </c>
-      <c r="C212" t="s">
-        <v>213</v>
-      </c>
-      <c r="D212" s="6">
-        <v>45782.913865740738</v>
-      </c>
-      <c r="E212" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F212" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G212">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A213" t="s">
-        <v>364</v>
-      </c>
-      <c r="B213" t="s">
-        <v>213</v>
-      </c>
-      <c r="C213" t="s">
-        <v>211</v>
-      </c>
-      <c r="D213" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E213" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F213" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G213">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A214" t="s">
-        <v>365</v>
-      </c>
-      <c r="B214" t="s">
-        <v>213</v>
-      </c>
-      <c r="C214" t="s">
-        <v>211</v>
-      </c>
-      <c r="D214" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E214" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F214" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G214">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A215" t="s">
-        <v>366</v>
-      </c>
-      <c r="B215" t="s">
-        <v>213</v>
-      </c>
-      <c r="C215" t="s">
-        <v>214</v>
-      </c>
-      <c r="D215" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E215" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F215" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G215">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A216" t="s">
-        <v>367</v>
-      </c>
-      <c r="B216" t="s">
-        <v>213</v>
-      </c>
-      <c r="C216" t="s">
-        <v>214</v>
-      </c>
-      <c r="D216" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E216" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F216" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A217" t="s">
-        <v>180</v>
-      </c>
-      <c r="B217" t="s">
-        <v>213</v>
-      </c>
-      <c r="C217" t="s">
-        <v>211</v>
-      </c>
-      <c r="D217" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E217" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F217" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G217">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A218" t="s">
-        <v>62</v>
-      </c>
-      <c r="B218" t="s">
-        <v>213</v>
-      </c>
-      <c r="C218" t="s">
-        <v>211</v>
-      </c>
-      <c r="D218" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E218" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F218" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G218">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A219" t="s">
-        <v>29</v>
-      </c>
-      <c r="B219" t="s">
-        <v>213</v>
-      </c>
-      <c r="C219" t="s">
-        <v>214</v>
-      </c>
-      <c r="D219" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E219" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F219" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G219">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A220" t="s">
-        <v>189</v>
-      </c>
-      <c r="B220" t="s">
-        <v>213</v>
-      </c>
-      <c r="C220" t="s">
-        <v>214</v>
-      </c>
-      <c r="D220" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E220" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F220" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G220">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A221" t="s">
-        <v>92</v>
-      </c>
-      <c r="B221" t="s">
-        <v>213</v>
-      </c>
-      <c r="C221" t="s">
-        <v>216</v>
-      </c>
-      <c r="D221" s="6">
-        <v>45782.932708333334</v>
-      </c>
-      <c r="E221" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F221" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G221">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A222" t="s">
-        <v>50</v>
-      </c>
-      <c r="B222" t="s">
-        <v>214</v>
-      </c>
-      <c r="C222" t="s">
-        <v>215</v>
-      </c>
-      <c r="D222" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E222" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F222" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G222">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A223" t="s">
-        <v>129</v>
-      </c>
-      <c r="B223" t="s">
-        <v>214</v>
-      </c>
-      <c r="C223" t="s">
-        <v>215</v>
-      </c>
-      <c r="D223" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E223" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F223" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G223">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A224" t="s">
-        <v>123</v>
-      </c>
-      <c r="B224" t="s">
-        <v>214</v>
-      </c>
-      <c r="C224" t="s">
-        <v>215</v>
-      </c>
-      <c r="D224" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E224" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F224" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G224">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A225" t="s">
-        <v>109</v>
-      </c>
-      <c r="B225" t="s">
-        <v>214</v>
-      </c>
-      <c r="C225" t="s">
-        <v>215</v>
-      </c>
-      <c r="D225" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E225" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F225" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G225">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A226" t="s">
-        <v>119</v>
-      </c>
-      <c r="B226" t="s">
-        <v>214</v>
-      </c>
-      <c r="C226" t="s">
-        <v>215</v>
-      </c>
-      <c r="D226" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E226" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F226" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G226">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A227" t="s">
-        <v>57</v>
-      </c>
-      <c r="B227" t="s">
-        <v>214</v>
-      </c>
-      <c r="C227" t="s">
-        <v>215</v>
-      </c>
-      <c r="D227" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E227" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F227" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G227">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A228" t="s">
-        <v>190</v>
-      </c>
-      <c r="B228" t="s">
-        <v>214</v>
-      </c>
-      <c r="C228" t="s">
-        <v>215</v>
-      </c>
-      <c r="D228" s="6">
-        <v>45782.934039351851</v>
-      </c>
-      <c r="E228" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F228" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G228">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A229" t="s">
-        <v>24</v>
-      </c>
-      <c r="B229" t="s">
-        <v>213</v>
-      </c>
-      <c r="C229" t="s">
-        <v>214</v>
-      </c>
-      <c r="D229" s="6">
-        <v>45782.934490740743</v>
-      </c>
-      <c r="E229" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F229" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G229">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A230" t="s">
-        <v>132</v>
-      </c>
-      <c r="B230" t="s">
-        <v>213</v>
-      </c>
-      <c r="C230" t="s">
-        <v>214</v>
-      </c>
-      <c r="D230" s="6">
-        <v>45782.934490740743</v>
-      </c>
-      <c r="E230" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F230" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G230">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A231" t="s">
-        <v>159</v>
-      </c>
-      <c r="B231" t="s">
-        <v>213</v>
-      </c>
-      <c r="C231" t="s">
-        <v>214</v>
-      </c>
-      <c r="D231" s="6">
-        <v>45782.942291666666</v>
-      </c>
-      <c r="E231" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F231" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G231">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A232" t="s">
-        <v>26</v>
-      </c>
-      <c r="B232" t="s">
-        <v>213</v>
-      </c>
-      <c r="C232" t="s">
-        <v>211</v>
-      </c>
-      <c r="D232" s="6">
-        <v>45782.942291666666</v>
-      </c>
-      <c r="E232" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F232" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G232">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A233" t="s">
-        <v>177</v>
-      </c>
-      <c r="B233" t="s">
-        <v>213</v>
-      </c>
-      <c r="C233" t="s">
-        <v>211</v>
-      </c>
-      <c r="D233" s="6">
-        <v>45782.942291666666</v>
-      </c>
-      <c r="E233" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F233" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G233">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A234" t="s">
-        <v>94</v>
-      </c>
-      <c r="B234" t="s">
-        <v>210</v>
-      </c>
-      <c r="C234" t="s">
-        <v>214</v>
-      </c>
-      <c r="D234" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E234" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F234" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G234">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A235" t="s">
-        <v>108</v>
-      </c>
-      <c r="B235" t="s">
-        <v>210</v>
-      </c>
-      <c r="C235" t="s">
-        <v>214</v>
-      </c>
-      <c r="D235" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E235" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F235" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G235">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A236" t="s">
-        <v>78</v>
-      </c>
-      <c r="B236" t="s">
-        <v>210</v>
-      </c>
-      <c r="C236" t="s">
-        <v>214</v>
-      </c>
-      <c r="D236" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E236" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F236" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G236">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A237" t="s">
-        <v>158</v>
-      </c>
-      <c r="B237" t="s">
-        <v>210</v>
-      </c>
-      <c r="C237" t="s">
-        <v>214</v>
-      </c>
-      <c r="D237" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E237" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F237" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G237">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A238" t="s">
-        <v>187</v>
-      </c>
-      <c r="B238" t="s">
-        <v>210</v>
-      </c>
-      <c r="C238" t="s">
-        <v>214</v>
-      </c>
-      <c r="D238" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E238" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F238" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G238">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A239" t="s">
-        <v>368</v>
-      </c>
-      <c r="B239" t="s">
-        <v>210</v>
-      </c>
-      <c r="C239" t="s">
-        <v>214</v>
-      </c>
-      <c r="D239" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E239" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F239" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G239">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A240" t="s">
-        <v>402</v>
-      </c>
-      <c r="B240" t="s">
-        <v>210</v>
-      </c>
-      <c r="C240" t="s">
-        <v>214</v>
-      </c>
-      <c r="D240" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E240" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F240" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G240">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A241" t="s">
-        <v>403</v>
-      </c>
-      <c r="B241" t="s">
-        <v>210</v>
-      </c>
-      <c r="C241" t="s">
-        <v>214</v>
-      </c>
-      <c r="D241" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E241" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F241" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G241">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A242" t="s">
-        <v>404</v>
-      </c>
-      <c r="B242" t="s">
-        <v>210</v>
-      </c>
-      <c r="C242" t="s">
-        <v>214</v>
-      </c>
-      <c r="D242" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E242" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F242" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G242">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A243" t="s">
-        <v>406</v>
-      </c>
-      <c r="B243" t="s">
-        <v>210</v>
-      </c>
-      <c r="C243" t="s">
-        <v>214</v>
-      </c>
-      <c r="D243" s="6">
-        <v>45782.943182870367</v>
-      </c>
-      <c r="E243" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F243" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G243">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A244" t="s">
-        <v>35</v>
-      </c>
-      <c r="B244" t="s">
-        <v>214</v>
-      </c>
-      <c r="C244" t="s">
-        <v>216</v>
-      </c>
-      <c r="D244" s="6">
-        <v>45782.945370370369</v>
-      </c>
-      <c r="E244" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F244" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G244">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A245" t="s">
-        <v>133</v>
-      </c>
-      <c r="B245" t="s">
-        <v>214</v>
-      </c>
-      <c r="C245" t="s">
-        <v>216</v>
-      </c>
-      <c r="D245" s="6">
-        <v>45782.945370370369</v>
-      </c>
-      <c r="E245" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F245" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G245">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A246" t="s">
-        <v>43</v>
-      </c>
-      <c r="B246" t="s">
-        <v>214</v>
-      </c>
-      <c r="C246" t="s">
-        <v>216</v>
-      </c>
-      <c r="D246" s="6">
-        <v>45782.945370370369</v>
-      </c>
-      <c r="E246" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F246" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G246">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A247" t="s">
-        <v>409</v>
-      </c>
-      <c r="B247" t="s">
-        <v>214</v>
-      </c>
-      <c r="C247" t="s">
-        <v>215</v>
-      </c>
-      <c r="D247" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E247" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F247" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G247">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A248" t="s">
-        <v>411</v>
-      </c>
-      <c r="B248" t="s">
-        <v>214</v>
-      </c>
-      <c r="C248" t="s">
-        <v>215</v>
-      </c>
-      <c r="D248" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E248" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F248" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G248">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" t="s">
-        <v>413</v>
-      </c>
-      <c r="B249" t="s">
-        <v>214</v>
-      </c>
-      <c r="C249" t="s">
-        <v>215</v>
-      </c>
-      <c r="D249" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E249" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F249" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G249">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" t="s">
-        <v>415</v>
-      </c>
-      <c r="B250" t="s">
-        <v>214</v>
-      </c>
-      <c r="C250" t="s">
-        <v>215</v>
-      </c>
-      <c r="D250" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E250" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F250" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G250">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" t="s">
-        <v>417</v>
-      </c>
-      <c r="B251" t="s">
-        <v>214</v>
-      </c>
-      <c r="C251" t="s">
-        <v>215</v>
-      </c>
-      <c r="D251" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E251" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F251" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G251">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A252" t="s">
-        <v>419</v>
-      </c>
-      <c r="B252" t="s">
-        <v>214</v>
-      </c>
-      <c r="C252" t="s">
-        <v>215</v>
-      </c>
-      <c r="D252" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E252" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F252" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G252">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A253" t="s">
-        <v>454</v>
-      </c>
-      <c r="B253" t="s">
-        <v>214</v>
-      </c>
-      <c r="C253" t="s">
-        <v>215</v>
-      </c>
-      <c r="D253" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E253" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F253" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G253">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A254" t="s">
-        <v>456</v>
-      </c>
-      <c r="B254" t="s">
-        <v>214</v>
-      </c>
-      <c r="C254" t="s">
-        <v>215</v>
-      </c>
-      <c r="D254" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E254" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F254" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G254">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A255" t="s">
-        <v>478</v>
-      </c>
-      <c r="B255" t="s">
-        <v>214</v>
-      </c>
-      <c r="C255" t="s">
-        <v>215</v>
-      </c>
-      <c r="D255" s="6">
-        <v>45782.949421296296</v>
-      </c>
-      <c r="E255" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F255" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G255">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A256" t="s">
-        <v>484</v>
-      </c>
-      <c r="B256" t="s">
-        <v>211</v>
-      </c>
-      <c r="C256" t="s">
-        <v>216</v>
-      </c>
-      <c r="D256" s="6">
-        <v>45782.951493055552</v>
-      </c>
-      <c r="E256" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F256" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G256">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A257" t="s">
-        <v>81</v>
-      </c>
-      <c r="B257" t="s">
-        <v>214</v>
-      </c>
-      <c r="C257" t="s">
-        <v>211</v>
-      </c>
-      <c r="D257" s="6">
-        <v>45782.952511574076</v>
-      </c>
-      <c r="E257" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F257" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G257">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A258" t="s">
-        <v>17</v>
-      </c>
-      <c r="B258" t="s">
-        <v>214</v>
-      </c>
-      <c r="C258" t="s">
-        <v>211</v>
-      </c>
-      <c r="D258" s="6">
-        <v>45782.952511574076</v>
-      </c>
-      <c r="E258" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F258" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G258">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A259" t="s">
-        <v>195</v>
-      </c>
-      <c r="B259" t="s">
-        <v>214</v>
-      </c>
-      <c r="C259" t="s">
-        <v>211</v>
-      </c>
-      <c r="D259" s="6">
-        <v>45782.952511574076</v>
-      </c>
-      <c r="E259" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F259" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G259">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A260" t="s">
-        <v>105</v>
-      </c>
-      <c r="B260" t="s">
-        <v>214</v>
-      </c>
-      <c r="C260" t="s">
-        <v>211</v>
-      </c>
-      <c r="D260" s="6">
-        <v>45782.952511574076</v>
-      </c>
-      <c r="E260" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F260" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G260">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A261" t="s">
-        <v>27</v>
-      </c>
-      <c r="B261" t="s">
-        <v>214</v>
-      </c>
-      <c r="C261" t="s">
-        <v>211</v>
-      </c>
-      <c r="D261" s="6">
-        <v>45782.952511574076</v>
-      </c>
-      <c r="E261" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F261" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G261">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A262" t="s">
-        <v>425</v>
-      </c>
-      <c r="B262" t="s">
-        <v>211</v>
-      </c>
-      <c r="C262" t="s">
-        <v>216</v>
-      </c>
-      <c r="D262" s="6">
-        <v>45782.955648148149</v>
-      </c>
-      <c r="E262" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F262" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G262">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A263" t="s">
-        <v>426</v>
-      </c>
-      <c r="B263" t="s">
-        <v>211</v>
-      </c>
-      <c r="C263" t="s">
-        <v>216</v>
-      </c>
-      <c r="D263" s="6">
-        <v>45782.955648148149</v>
-      </c>
-      <c r="E263" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F263" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G263">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A264" t="s">
-        <v>427</v>
-      </c>
-      <c r="B264" t="s">
-        <v>211</v>
-      </c>
-      <c r="C264" t="s">
-        <v>216</v>
-      </c>
-      <c r="D264" s="6">
-        <v>45782.955648148149</v>
-      </c>
-      <c r="E264" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F264" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G264">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A265" t="s">
-        <v>55</v>
-      </c>
-      <c r="B265" t="s">
-        <v>211</v>
-      </c>
-      <c r="C265" t="s">
-        <v>216</v>
-      </c>
-      <c r="D265" s="6">
-        <v>45782.957129629627</v>
-      </c>
-      <c r="E265" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F265" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G265">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A266" t="s">
-        <v>19</v>
-      </c>
-      <c r="B266" t="s">
-        <v>211</v>
-      </c>
-      <c r="C266" t="s">
-        <v>216</v>
-      </c>
-      <c r="D266" s="6">
-        <v>45782.957129629627</v>
-      </c>
-      <c r="E266" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F266" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G266">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A267" t="s">
-        <v>173</v>
-      </c>
-      <c r="B267" t="s">
-        <v>211</v>
-      </c>
-      <c r="C267" t="s">
-        <v>216</v>
-      </c>
-      <c r="D267" s="6">
-        <v>45782.957129629627</v>
-      </c>
-      <c r="E267" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F267" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G267">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A268" t="s">
-        <v>196</v>
-      </c>
-      <c r="B268" t="s">
-        <v>211</v>
-      </c>
-      <c r="C268" t="s">
-        <v>216</v>
-      </c>
-      <c r="D268" s="6">
-        <v>45782.957129629627</v>
-      </c>
-      <c r="E268" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F268" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G268">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A269" t="s">
-        <v>200</v>
-      </c>
-      <c r="B269" t="s">
-        <v>208</v>
-      </c>
-      <c r="C269" t="s">
-        <v>211</v>
-      </c>
-      <c r="D269" s="6">
-        <v>45782.95853009259</v>
-      </c>
-      <c r="E269" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F269" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G269">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A270" t="s">
-        <v>68</v>
-      </c>
-      <c r="B270" t="s">
-        <v>208</v>
-      </c>
-      <c r="C270" t="s">
-        <v>211</v>
-      </c>
-      <c r="D270" s="6">
-        <v>45782.95853009259</v>
-      </c>
-      <c r="E270" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="F270" s="8">
-        <v>0.125</v>
-      </c>
-      <c r="G270">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A271" t="s">
-        <v>395</v>
-      </c>
-      <c r="B271" t="s">
-        <v>208</v>
-      </c>
-      <c r="C271" t="s">
-        <v>211</v>
-      </c>
-      <c r="D271" s="6">
-        <v>45782.95853009259</v>
-      </c>
-      <c r="E271" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F271" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G271">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A272" t="s">
-        <v>202</v>
-      </c>
-      <c r="B272" t="s">
-        <v>208</v>
-      </c>
-      <c r="C272" t="s">
-        <v>211</v>
-      </c>
-      <c r="D272" s="6">
-        <v>45782.95853009259</v>
-      </c>
-      <c r="E272" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F272" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G272">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>182</v>
-      </c>
-      <c r="B273" t="s">
-        <v>214</v>
-      </c>
-      <c r="C273" t="s">
-        <v>211</v>
-      </c>
-      <c r="D273" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E273" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F273" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G273">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A274" t="s">
-        <v>51</v>
-      </c>
-      <c r="B274" t="s">
-        <v>214</v>
-      </c>
-      <c r="C274" t="s">
-        <v>211</v>
-      </c>
-      <c r="D274" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E274" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F274" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G274">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A275" t="s">
-        <v>130</v>
-      </c>
-      <c r="B275" t="s">
-        <v>214</v>
-      </c>
-      <c r="C275" t="s">
-        <v>211</v>
-      </c>
-      <c r="D275" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E275" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F275" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G275">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A276" t="s">
-        <v>10</v>
-      </c>
-      <c r="B276" t="s">
-        <v>214</v>
-      </c>
-      <c r="C276" t="s">
-        <v>211</v>
-      </c>
-      <c r="D276" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E276" s="8">
-        <v>0.15</v>
-      </c>
-      <c r="F276" s="8">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G276">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A277" t="s">
-        <v>388</v>
-      </c>
-      <c r="B277" t="s">
-        <v>214</v>
-      </c>
-      <c r="C277" t="s">
-        <v>211</v>
-      </c>
-      <c r="D277" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E277" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F277" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G277">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A278" t="s">
-        <v>389</v>
-      </c>
-      <c r="B278" t="s">
-        <v>214</v>
-      </c>
-      <c r="C278" t="s">
-        <v>211</v>
-      </c>
-      <c r="D278" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E278" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F278" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G278">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A279" t="s">
-        <v>390</v>
-      </c>
-      <c r="B279" t="s">
-        <v>214</v>
-      </c>
-      <c r="C279" t="s">
-        <v>211</v>
-      </c>
-      <c r="D279" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E279" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F279" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G279">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" t="s">
-        <v>391</v>
-      </c>
-      <c r="B280" t="s">
-        <v>214</v>
-      </c>
-      <c r="C280" t="s">
-        <v>211</v>
-      </c>
-      <c r="D280" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E280" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F280" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G280">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" t="s">
-        <v>392</v>
-      </c>
-      <c r="B281" t="s">
-        <v>214</v>
-      </c>
-      <c r="C281" t="s">
-        <v>211</v>
-      </c>
-      <c r="D281" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E281" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F281" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G281">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" t="s">
-        <v>393</v>
-      </c>
-      <c r="B282" t="s">
-        <v>214</v>
-      </c>
-      <c r="C282" t="s">
-        <v>211</v>
-      </c>
-      <c r="D282" s="6">
-        <v>45782.960717592592</v>
-      </c>
-      <c r="E282" s="8">
-        <v>0.2</v>
-      </c>
-      <c r="F282" s="8">
-        <v>0.1</v>
-      </c>
-      <c r="G282">
-        <v>2</v>
+      <c r="G5" s="10">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G282">
+  <autoFilter ref="A1:G2">
     <sortState ref="A2:G282">
       <sortCondition ref="D1:D282"/>
     </sortState>
@@ -8477,7 +1913,7 @@
         <v>211</v>
       </c>
       <c r="C2" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D2" s="6">
         <v>45782.057719907411</v>
@@ -8500,7 +1936,7 @@
         <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D3" s="6">
         <v>45782.09611111111</v>
@@ -8523,7 +1959,7 @@
         <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D4" s="6">
         <v>45782.187175925923</v>
@@ -8546,7 +1982,7 @@
         <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="D5" s="6">
         <v>45782.279652777775</v>
@@ -8592,7 +2028,7 @@
         <v>211</v>
       </c>
       <c r="C7" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D7" s="6">
         <v>45782.306250000001</v>
@@ -8615,7 +2051,7 @@
         <v>211</v>
       </c>
       <c r="C8" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D8" s="6">
         <v>45782.328923611109</v>
@@ -8638,7 +2074,7 @@
         <v>210</v>
       </c>
       <c r="C9" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D9" s="6">
         <v>45782.368078703701</v>
@@ -8704,7 +2140,7 @@
         <v>199</v>
       </c>
       <c r="B12" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C12" t="s">
         <v>206</v>
@@ -8727,7 +2163,7 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C13" t="s">
         <v>206</v>
@@ -8750,7 +2186,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C14" t="s">
         <v>211</v>
@@ -8773,7 +2209,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C15" t="s">
         <v>211</v>
@@ -8799,7 +2235,7 @@
         <v>218</v>
       </c>
       <c r="C16" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D16" s="6">
         <v>45782.439895833333</v>
@@ -8822,7 +2258,7 @@
         <v>218</v>
       </c>
       <c r="C17" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D17" s="6">
         <v>45782.439895833333</v>
@@ -8845,7 +2281,7 @@
         <v>218</v>
       </c>
       <c r="C18" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D18" s="6">
         <v>45782.439895833333</v>
@@ -8868,7 +2304,7 @@
         <v>218</v>
       </c>
       <c r="C19" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D19" s="6">
         <v>45782.439895833333</v>
@@ -8891,7 +2327,7 @@
         <v>218</v>
       </c>
       <c r="C20" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D20" s="6">
         <v>45782.439895833333</v>
@@ -8914,7 +2350,7 @@
         <v>218</v>
       </c>
       <c r="C21" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D21" s="6">
         <v>45782.439895833333</v>
@@ -8937,7 +2373,7 @@
         <v>218</v>
       </c>
       <c r="C22" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D22" s="6">
         <v>45782.439895833333</v>
@@ -8960,7 +2396,7 @@
         <v>218</v>
       </c>
       <c r="C23" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D23" s="6">
         <v>45782.439895833333</v>
@@ -8983,7 +2419,7 @@
         <v>218</v>
       </c>
       <c r="C24" t="s">
-        <v>493</v>
+        <v>425</v>
       </c>
       <c r="D24" s="6">
         <v>45782.439895833333</v>
@@ -9006,7 +2442,7 @@
         <v>218</v>
       </c>
       <c r="C25" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D25" s="6">
         <v>45782.452106481483</v>
@@ -9121,7 +2557,7 @@
         <v>211</v>
       </c>
       <c r="C30" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D30" s="6">
         <v>45782.53261574074</v>
@@ -9141,10 +2577,10 @@
         <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C31" t="s">
-        <v>495</v>
+        <v>427</v>
       </c>
       <c r="D31" s="6">
         <v>45782.542268518519</v>
@@ -9164,10 +2600,10 @@
         <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C32" t="s">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="D32" s="6">
         <v>45782.551261574074</v>
@@ -9187,10 +2623,10 @@
         <v>143</v>
       </c>
       <c r="B33" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C33" t="s">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="D33" s="6">
         <v>45782.551261574074</v>
@@ -9210,10 +2646,10 @@
         <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C34" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D34" s="6">
         <v>45782.58792824074</v>
@@ -9233,10 +2669,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C35" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D35" s="6">
         <v>45782.58792824074</v>
@@ -9256,10 +2692,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C36" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D36" s="6">
         <v>45782.58792824074</v>
@@ -9279,10 +2715,10 @@
         <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C37" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D37" s="6">
         <v>45782.58792824074</v>
@@ -9302,10 +2738,10 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C38" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D38" s="6">
         <v>45782.58792824074</v>
@@ -9325,10 +2761,10 @@
         <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C39" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D39" s="6">
         <v>45782.58792824074</v>
@@ -9348,7 +2784,7 @@
         <v>201</v>
       </c>
       <c r="B40" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C40" t="s">
         <v>206</v>
@@ -9371,7 +2807,7 @@
         <v>196</v>
       </c>
       <c r="B41" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
         <v>206</v>
@@ -9420,7 +2856,7 @@
         <v>210</v>
       </c>
       <c r="C43" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D43" s="6">
         <v>45782.604513888888</v>
@@ -9440,10 +2876,10 @@
         <v>205</v>
       </c>
       <c r="B44" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C44" t="s">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="D44" s="6">
         <v>45782.606215277781</v>
@@ -9466,7 +2902,7 @@
         <v>208</v>
       </c>
       <c r="C45" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="D45" s="6">
         <v>45782.606493055559</v>
@@ -9489,7 +2925,7 @@
         <v>218</v>
       </c>
       <c r="C46" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D46" s="6">
         <v>45782.606608796297</v>
@@ -9509,10 +2945,10 @@
         <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C47" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D47" s="6">
         <v>45782.608865740738</v>
@@ -9532,10 +2968,10 @@
         <v>58</v>
       </c>
       <c r="B48" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C48" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D48" s="6">
         <v>45782.608865740738</v>
@@ -9555,10 +2991,10 @@
         <v>29</v>
       </c>
       <c r="B49" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C49" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D49" s="6">
         <v>45782.608865740738</v>
@@ -9578,10 +3014,10 @@
         <v>189</v>
       </c>
       <c r="B50" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C50" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D50" s="6">
         <v>45782.608865740738</v>
@@ -9903,7 +3339,7 @@
         <v>212</v>
       </c>
       <c r="C64" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="D64" s="6">
         <v>45782.615162037036</v>
@@ -9972,7 +3408,7 @@
         <v>218</v>
       </c>
       <c r="C67" t="s">
-        <v>496</v>
+        <v>428</v>
       </c>
       <c r="D67" s="6">
         <v>45782.615902777776</v>
@@ -10110,7 +3546,7 @@
         <v>211</v>
       </c>
       <c r="C73" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D73" s="6">
         <v>45782.622060185182</v>
@@ -10133,7 +3569,7 @@
         <v>218</v>
       </c>
       <c r="C74" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D74" s="6">
         <v>45782.655555555553</v>
@@ -10156,7 +3592,7 @@
         <v>218</v>
       </c>
       <c r="C75" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D75" s="6">
         <v>45782.658125000002</v>
@@ -10179,7 +3615,7 @@
         <v>211</v>
       </c>
       <c r="C76" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D76" s="6">
         <v>45782.677361111113</v>
@@ -10202,7 +3638,7 @@
         <v>218</v>
       </c>
       <c r="C77" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D77" s="6">
         <v>45782.691574074073</v>
@@ -10225,7 +3661,7 @@
         <v>218</v>
       </c>
       <c r="C78" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D78" s="6">
         <v>45782.691574074073</v>
@@ -10248,7 +3684,7 @@
         <v>218</v>
       </c>
       <c r="C79" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D79" s="6">
         <v>45782.691574074073</v>
@@ -10271,7 +3707,7 @@
         <v>218</v>
       </c>
       <c r="C80" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D80" s="6">
         <v>45782.691574074073</v>
@@ -10294,7 +3730,7 @@
         <v>218</v>
       </c>
       <c r="C81" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D81" s="6">
         <v>45782.691574074073</v>
@@ -10317,7 +3753,7 @@
         <v>218</v>
       </c>
       <c r="C82" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D82" s="6">
         <v>45782.691574074073</v>
@@ -10340,7 +3776,7 @@
         <v>218</v>
       </c>
       <c r="C83" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D83" s="6">
         <v>45782.691574074073</v>
@@ -10363,7 +3799,7 @@
         <v>218</v>
       </c>
       <c r="C84" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D84" s="6">
         <v>45782.691574074073</v>
@@ -10386,7 +3822,7 @@
         <v>218</v>
       </c>
       <c r="C85" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D85" s="6">
         <v>45782.691574074073</v>
@@ -10409,7 +3845,7 @@
         <v>218</v>
       </c>
       <c r="C86" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D86" s="6">
         <v>45782.691574074073</v>
@@ -10429,10 +3865,10 @@
         <v>112</v>
       </c>
       <c r="B87" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C87" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D87" s="6">
         <v>45782.696736111109</v>
@@ -10455,7 +3891,7 @@
         <v>211</v>
       </c>
       <c r="C88" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D88" s="6">
         <v>45782.706284722219</v>
@@ -10524,7 +3960,7 @@
         <v>216</v>
       </c>
       <c r="C91" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D91" s="6">
         <v>45782.720254629632</v>
@@ -10570,7 +4006,7 @@
         <v>218</v>
       </c>
       <c r="C93" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D93" s="6">
         <v>45782.731828703705</v>
@@ -10705,10 +4141,10 @@
         <v>38</v>
       </c>
       <c r="B99" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C99" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D99" s="6">
         <v>45782.76630787037</v>
@@ -10728,10 +4164,10 @@
         <v>14</v>
       </c>
       <c r="B100" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C100" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D100" s="6">
         <v>45782.800810185188</v>
@@ -10751,10 +4187,10 @@
         <v>64</v>
       </c>
       <c r="B101" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C101" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D101" s="6">
         <v>45782.800810185188</v>
@@ -10777,7 +4213,7 @@
         <v>211</v>
       </c>
       <c r="C102" t="s">
-        <v>487</v>
+        <v>419</v>
       </c>
       <c r="D102" s="6">
         <v>45782.813935185186</v>
@@ -10800,7 +4236,7 @@
         <v>206</v>
       </c>
       <c r="C103" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="D103" s="6">
         <v>45782.81554398148</v>
@@ -10823,7 +4259,7 @@
         <v>207</v>
       </c>
       <c r="C104" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D104" s="6">
         <v>45782.822476851848</v>
@@ -10846,7 +4282,7 @@
         <v>207</v>
       </c>
       <c r="C105" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D105" s="6">
         <v>45782.822476851848</v>
@@ -10869,7 +4305,7 @@
         <v>207</v>
       </c>
       <c r="C106" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D106" s="6">
         <v>45782.822476851848</v>
@@ -10892,7 +4328,7 @@
         <v>207</v>
       </c>
       <c r="C107" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D107" s="6">
         <v>45782.822476851848</v>
@@ -10915,7 +4351,7 @@
         <v>207</v>
       </c>
       <c r="C108" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D108" s="6">
         <v>45782.822476851848</v>
@@ -10938,7 +4374,7 @@
         <v>207</v>
       </c>
       <c r="C109" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D109" s="6">
         <v>45782.822476851848</v>
@@ -10961,7 +4397,7 @@
         <v>207</v>
       </c>
       <c r="C110" t="s">
-        <v>494</v>
+        <v>426</v>
       </c>
       <c r="D110" s="6">
         <v>45782.822476851848</v>
@@ -11188,10 +4624,10 @@
         <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C120" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D120" s="6">
         <v>45782.9221875</v>
@@ -11211,10 +4647,10 @@
         <v>195</v>
       </c>
       <c r="B121" t="s">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="C121" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D121" s="6">
         <v>45782.934791666667</v>
@@ -11234,10 +4670,10 @@
         <v>105</v>
       </c>
       <c r="B122" t="s">
-        <v>490</v>
+        <v>422</v>
       </c>
       <c r="C122" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D122" s="6">
         <v>45782.934791666667</v>
@@ -11283,7 +4719,7 @@
         <v>206</v>
       </c>
       <c r="C124" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D124" s="6">
         <v>45782.936736111114</v>
@@ -11306,7 +4742,7 @@
         <v>206</v>
       </c>
       <c r="C125" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D125" s="6">
         <v>45782.936747685184</v>
@@ -11329,7 +4765,7 @@
         <v>210</v>
       </c>
       <c r="C126" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D126" s="6">
         <v>45782.940324074072</v>
@@ -11651,7 +5087,7 @@
         <v>210</v>
       </c>
       <c r="C140" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D140" s="6">
         <v>45782.940324074072</v>
@@ -11674,7 +5110,7 @@
         <v>210</v>
       </c>
       <c r="C141" t="s">
-        <v>492</v>
+        <v>424</v>
       </c>
       <c r="D141" s="6">
         <v>45782.940324074072</v>
@@ -12157,7 +5593,7 @@
         <v>210</v>
       </c>
       <c r="C162" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D162" s="6">
         <v>45782.940324074072</v>
@@ -12180,7 +5616,7 @@
         <v>210</v>
       </c>
       <c r="C163" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D163" s="6">
         <v>45782.940324074072</v>
@@ -12249,7 +5685,7 @@
         <v>210</v>
       </c>
       <c r="C166" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D166" s="6">
         <v>45782.940324074072</v>
@@ -12916,7 +6352,7 @@
         <v>206</v>
       </c>
       <c r="C195" t="s">
-        <v>488</v>
+        <v>420</v>
       </c>
       <c r="D195" s="6">
         <v>45782.94767361111</v>
@@ -13005,10 +6441,10 @@
         <v>44</v>
       </c>
       <c r="B199" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C199" t="s">
-        <v>496</v>
+        <v>428</v>
       </c>
       <c r="D199" s="6">
         <v>45782.948634259257</v>
@@ -13028,10 +6464,10 @@
         <v>140</v>
       </c>
       <c r="B200" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C200" t="s">
-        <v>496</v>
+        <v>428</v>
       </c>
       <c r="D200" s="6">
         <v>45782.948634259257</v>
@@ -13051,7 +6487,7 @@
         <v>163</v>
       </c>
       <c r="B201" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="C201" t="s">
         <v>214</v>
@@ -13192,7 +6628,7 @@
         <v>216</v>
       </c>
       <c r="C207" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D207" s="6">
         <v>45782.954930555556</v>
@@ -13215,7 +6651,7 @@
         <v>216</v>
       </c>
       <c r="C208" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D208" s="6">
         <v>45782.954930555556</v>
@@ -13238,7 +6674,7 @@
         <v>216</v>
       </c>
       <c r="C209" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D209" s="6">
         <v>45782.954930555556</v>
@@ -13284,7 +6720,7 @@
         <v>216</v>
       </c>
       <c r="C211" t="s">
-        <v>489</v>
+        <v>421</v>
       </c>
       <c r="D211" s="6">
         <v>45782.954930555556</v>
@@ -13330,7 +6766,7 @@
         <v>216</v>
       </c>
       <c r="C213" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D213" s="6">
         <v>45782.954930555556</v>
@@ -13353,7 +6789,7 @@
         <v>216</v>
       </c>
       <c r="C214" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D214" s="6">
         <v>45782.954930555556</v>
@@ -13376,7 +6812,7 @@
         <v>216</v>
       </c>
       <c r="C215" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D215" s="6">
         <v>45782.954930555556</v>
@@ -13468,7 +6904,7 @@
         <v>216</v>
       </c>
       <c r="C219" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D219" s="6">
         <v>45782.954930555556</v>
@@ -13491,7 +6927,7 @@
         <v>216</v>
       </c>
       <c r="C220" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D220" s="6">
         <v>45782.954930555556</v>
@@ -13583,7 +7019,7 @@
         <v>216</v>
       </c>
       <c r="C224" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D224" s="6">
         <v>45782.954930555556</v>
@@ -13606,7 +7042,7 @@
         <v>216</v>
       </c>
       <c r="C225" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D225" s="6">
         <v>45782.954930555556</v>
@@ -13629,7 +7065,7 @@
         <v>216</v>
       </c>
       <c r="C226" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D226" s="6">
         <v>45782.954930555556</v>
@@ -13652,7 +7088,7 @@
         <v>216</v>
       </c>
       <c r="C227" t="s">
-        <v>491</v>
+        <v>423</v>
       </c>
       <c r="D227" s="6">
         <v>45782.954930555556</v>
@@ -19108,15 +12544,15 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
-        <v>500</v>
+        <v>432</v>
       </c>
       <c r="C1" t="s">
-        <v>501</v>
+        <v>433</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>497</v>
+        <v>429</v>
       </c>
       <c r="B2" s="7">
         <v>0.25</v>
@@ -19127,7 +12563,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>498</v>
+        <v>430</v>
       </c>
       <c r="B3" s="7">
         <v>0.2</v>
@@ -19138,7 +12574,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>499</v>
+        <v>431</v>
       </c>
       <c r="B4" s="7">
         <v>0.15</v>

--- a/inputs/products.xlsx
+++ b/inputs/products.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\Er\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\GitHub\internal-logistics-model2\internal-logistics-model2\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9396"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5664"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="97">
   <si>
     <t>product_id</t>
   </si>
@@ -180,6 +180,141 @@
   </si>
   <si>
     <t>N30</t>
+  </si>
+  <si>
+    <t>P16</t>
+  </si>
+  <si>
+    <t>P17</t>
+  </si>
+  <si>
+    <t>P18</t>
+  </si>
+  <si>
+    <t>P19</t>
+  </si>
+  <si>
+    <t>P20</t>
+  </si>
+  <si>
+    <t>P21</t>
+  </si>
+  <si>
+    <t>P22</t>
+  </si>
+  <si>
+    <t>P23</t>
+  </si>
+  <si>
+    <t>P24</t>
+  </si>
+  <si>
+    <t>P25</t>
+  </si>
+  <si>
+    <t>P26</t>
+  </si>
+  <si>
+    <t>P27</t>
+  </si>
+  <si>
+    <t>P28</t>
+  </si>
+  <si>
+    <t>P29</t>
+  </si>
+  <si>
+    <t>P30</t>
+  </si>
+  <si>
+    <t>N31</t>
+  </si>
+  <si>
+    <t>N33</t>
+  </si>
+  <si>
+    <t>N35</t>
+  </si>
+  <si>
+    <t>N37</t>
+  </si>
+  <si>
+    <t>N39</t>
+  </si>
+  <si>
+    <t>N41</t>
+  </si>
+  <si>
+    <t>N43</t>
+  </si>
+  <si>
+    <t>N45</t>
+  </si>
+  <si>
+    <t>N47</t>
+  </si>
+  <si>
+    <t>N49</t>
+  </si>
+  <si>
+    <t>N51</t>
+  </si>
+  <si>
+    <t>N53</t>
+  </si>
+  <si>
+    <t>N55</t>
+  </si>
+  <si>
+    <t>N57</t>
+  </si>
+  <si>
+    <t>N59</t>
+  </si>
+  <si>
+    <t>N32</t>
+  </si>
+  <si>
+    <t>N34</t>
+  </si>
+  <si>
+    <t>N36</t>
+  </si>
+  <si>
+    <t>N38</t>
+  </si>
+  <si>
+    <t>N40</t>
+  </si>
+  <si>
+    <t>N42</t>
+  </si>
+  <si>
+    <t>N44</t>
+  </si>
+  <si>
+    <t>N46</t>
+  </si>
+  <si>
+    <t>N48</t>
+  </si>
+  <si>
+    <t>N50</t>
+  </si>
+  <si>
+    <t>N52</t>
+  </si>
+  <si>
+    <t>N54</t>
+  </si>
+  <si>
+    <t>N56</t>
+  </si>
+  <si>
+    <t>N58</t>
+  </si>
+  <si>
+    <t>N60</t>
   </si>
 </sst>
 </file>
@@ -562,7 +697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -940,6 +1075,351 @@
         <v>20</v>
       </c>
     </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="2">
+        <v>65</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="2">
+        <v>70</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D20" s="2">
+        <v>75</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="2">
+        <v>80</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="2">
+        <v>85</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2">
+        <v>90</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D24" s="2">
+        <v>95</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="2">
+        <v>100</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="2">
+        <v>105</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" s="2">
+        <v>110</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2">
+        <v>115</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="2">
+        <v>120</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="2">
+        <v>125</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="2">
+        <v>130</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -947,7 +1427,744 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="3">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3">
+        <v>25</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="3">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
+        <v>48</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2">
+        <v>23</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>31</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="2">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="2">
+        <v>30</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="2">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="2">
+        <v>24</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="2">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="2">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="2">
+        <v>20</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="2">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="2">
+        <v>40</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" s="2">
+        <v>25</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2">
+        <v>45</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D22" s="2">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2">
+        <v>30</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="2">
+        <v>42</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" s="2">
+        <v>15</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="2">
+        <v>27</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27" s="2">
+        <v>38</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="2">
+        <v>50</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="2">
+        <v>22</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="2">
+        <v>44</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="2">
+        <v>16</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G9">
+    <sortState ref="A2:G12">
+      <sortCondition ref="A1:A11"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -981,25 +2198,25 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="3">
         <v>20</v>
       </c>
-      <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2">
-        <v>1</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
         <v>3</v>
       </c>
     </row>
@@ -1008,13 +2225,13 @@
         <v>8</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="3">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E3" s="3">
         <v>2</v>
@@ -1031,13 +2248,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -1054,13 +2271,13 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D5" s="3">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E5" s="3">
         <v>2</v>
@@ -1069,7 +2286,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1077,13 +2294,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="D6" s="3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3">
         <v>2</v>
@@ -1092,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1100,13 +2317,13 @@
         <v>12</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2">
         <v>2</v>
@@ -1123,13 +2340,13 @@
         <v>25</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2">
         <v>2</v>
@@ -1146,13 +2363,13 @@
         <v>26</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D9" s="2">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E9" s="2">
         <v>2</v>
@@ -1169,7 +2386,7 @@
         <v>27</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>21</v>
@@ -1192,7 +2409,7 @@
         <v>28</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>16</v>
@@ -1215,7 +2432,7 @@
         <v>37</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>22</v>
@@ -1238,13 +2455,13 @@
         <v>40</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D13" s="2">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2">
         <v>2</v>
@@ -1261,13 +2478,13 @@
         <v>43</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="E14" s="2">
         <v>2</v>
@@ -1284,13 +2501,13 @@
         <v>46</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="2">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2">
         <v>2</v>
@@ -1307,402 +2524,12 @@
         <v>49</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="2">
-        <v>24</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2</v>
-      </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G9">
-    <sortState ref="A2:G12">
-      <sortCondition ref="A1:A11"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="3">
-        <v>20</v>
-      </c>
-      <c r="E2" s="3">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="3">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="3">
-        <v>55</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="3">
-        <v>60</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1</v>
-      </c>
-      <c r="G6" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="2">
-        <v>40</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2</v>
-      </c>
-      <c r="F7" s="2">
-        <v>1</v>
-      </c>
-      <c r="G7" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2">
-        <v>2</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" s="2">
-        <v>28</v>
-      </c>
-      <c r="E9" s="2">
-        <v>2</v>
-      </c>
-      <c r="F9" s="2">
-        <v>1</v>
-      </c>
-      <c r="G9" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="2">
-        <v>52</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2">
-        <v>30</v>
-      </c>
-      <c r="E11" s="2">
-        <v>2</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="2">
-        <v>8</v>
-      </c>
-      <c r="E12" s="2">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="2">
-        <v>44</v>
-      </c>
-      <c r="E13" s="2">
-        <v>2</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D14" s="2">
-        <v>54</v>
-      </c>
-      <c r="E14" s="2">
-        <v>2</v>
-      </c>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="2">
-        <v>65</v>
-      </c>
-      <c r="E15" s="2">
-        <v>2</v>
-      </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="2">
         <v>87</v>
       </c>
       <c r="E16" s="2">
@@ -1713,6 +2540,351 @@
       </c>
       <c r="G16" s="2">
         <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2">
+        <v>35</v>
+      </c>
+      <c r="E18" s="2">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="2">
+        <v>22</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="2">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="2">
+        <v>60</v>
+      </c>
+      <c r="E21" s="2">
+        <v>2</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="2">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="2">
+        <v>38</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="2">
+        <v>55</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D25" s="2">
+        <v>25</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="2">
+        <v>42</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="2">
+        <v>63</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="2">
+        <v>30</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="2">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="2">
+        <v>72</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="2">
+        <v>80</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/inputs/products.xlsx
+++ b/inputs/products.xlsx
@@ -9,22 +9,24 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5664"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5664" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="case1" sheetId="1" r:id="rId1"/>
     <sheet name="case2" sheetId="2" r:id="rId2"/>
     <sheet name="case3" sheetId="3" r:id="rId3"/>
+    <sheet name="case4" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">case2!$A$1:$G$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">case4!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="176">
   <si>
     <t>product_id</t>
   </si>
@@ -315,6 +317,243 @@
   </si>
   <si>
     <t>N60</t>
+  </si>
+  <si>
+    <t>P31</t>
+  </si>
+  <si>
+    <t>P32</t>
+  </si>
+  <si>
+    <t>P33</t>
+  </si>
+  <si>
+    <t>P34</t>
+  </si>
+  <si>
+    <t>P35</t>
+  </si>
+  <si>
+    <t>P36</t>
+  </si>
+  <si>
+    <t>P37</t>
+  </si>
+  <si>
+    <t>P38</t>
+  </si>
+  <si>
+    <t>P39</t>
+  </si>
+  <si>
+    <t>P40</t>
+  </si>
+  <si>
+    <t>P41</t>
+  </si>
+  <si>
+    <t>P42</t>
+  </si>
+  <si>
+    <t>P43</t>
+  </si>
+  <si>
+    <t>P44</t>
+  </si>
+  <si>
+    <t>P45</t>
+  </si>
+  <si>
+    <t>P46</t>
+  </si>
+  <si>
+    <t>P47</t>
+  </si>
+  <si>
+    <t>P48</t>
+  </si>
+  <si>
+    <t>P49</t>
+  </si>
+  <si>
+    <t>P50</t>
+  </si>
+  <si>
+    <t>P51</t>
+  </si>
+  <si>
+    <t>P52</t>
+  </si>
+  <si>
+    <t>P53</t>
+  </si>
+  <si>
+    <t>P54</t>
+  </si>
+  <si>
+    <t>P55</t>
+  </si>
+  <si>
+    <t>P56</t>
+  </si>
+  <si>
+    <t>P57</t>
+  </si>
+  <si>
+    <t>P58</t>
+  </si>
+  <si>
+    <t>P59</t>
+  </si>
+  <si>
+    <t>P60</t>
+  </si>
+  <si>
+    <t>P61</t>
+  </si>
+  <si>
+    <t>P62</t>
+  </si>
+  <si>
+    <t>P63</t>
+  </si>
+  <si>
+    <t>P64</t>
+  </si>
+  <si>
+    <t>P65</t>
+  </si>
+  <si>
+    <t>P66</t>
+  </si>
+  <si>
+    <t>P67</t>
+  </si>
+  <si>
+    <t>P68</t>
+  </si>
+  <si>
+    <t>P69</t>
+  </si>
+  <si>
+    <t>P70</t>
+  </si>
+  <si>
+    <t>P71</t>
+  </si>
+  <si>
+    <t>P72</t>
+  </si>
+  <si>
+    <t>P73</t>
+  </si>
+  <si>
+    <t>P74</t>
+  </si>
+  <si>
+    <t>P75</t>
+  </si>
+  <si>
+    <t>P76</t>
+  </si>
+  <si>
+    <t>P77</t>
+  </si>
+  <si>
+    <t>P78</t>
+  </si>
+  <si>
+    <t>P79</t>
+  </si>
+  <si>
+    <t>P80</t>
+  </si>
+  <si>
+    <t>P81</t>
+  </si>
+  <si>
+    <t>P82</t>
+  </si>
+  <si>
+    <t>P83</t>
+  </si>
+  <si>
+    <t>P84</t>
+  </si>
+  <si>
+    <t>P85</t>
+  </si>
+  <si>
+    <t>P86</t>
+  </si>
+  <si>
+    <t>P87</t>
+  </si>
+  <si>
+    <t>P88</t>
+  </si>
+  <si>
+    <t>P89</t>
+  </si>
+  <si>
+    <t>P90</t>
+  </si>
+  <si>
+    <t>P91</t>
+  </si>
+  <si>
+    <t>P92</t>
+  </si>
+  <si>
+    <t>P93</t>
+  </si>
+  <si>
+    <t>P94</t>
+  </si>
+  <si>
+    <t>P95</t>
+  </si>
+  <si>
+    <t>P96</t>
+  </si>
+  <si>
+    <t>P97</t>
+  </si>
+  <si>
+    <t>P98</t>
+  </si>
+  <si>
+    <t>P99</t>
+  </si>
+  <si>
+    <t>P100</t>
+  </si>
+  <si>
+    <t>N09</t>
+  </si>
+  <si>
+    <t>N06</t>
+  </si>
+  <si>
+    <t>N04</t>
+  </si>
+  <si>
+    <t>N03</t>
+  </si>
+  <si>
+    <t>N05</t>
+  </si>
+  <si>
+    <t>N02</t>
+  </si>
+  <si>
+    <t>N07</t>
+  </si>
+  <si>
+    <t>N08</t>
+  </si>
+  <si>
+    <t>N01</t>
   </si>
 </sst>
 </file>
@@ -384,7 +623,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -393,6 +632,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -700,11 +942,13 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2167,11 +2411,13 @@
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2890,4 +3136,2351 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G101"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="2">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D4" s="2">
+        <v>12</v>
+      </c>
+      <c r="E4" s="2">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" s="2">
+        <v>14</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2">
+        <v>15</v>
+      </c>
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2">
+        <v>2</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3">
+        <v>20</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>22</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="2">
+        <v>22</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="2">
+        <v>24</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="2">
+        <v>25</v>
+      </c>
+      <c r="E12" s="2">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="2">
+        <v>28</v>
+      </c>
+      <c r="E13" s="2">
+        <v>2</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="2">
+        <v>29</v>
+      </c>
+      <c r="E14" s="2">
+        <v>2</v>
+      </c>
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D15" s="2">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2">
+        <v>30</v>
+      </c>
+      <c r="E16" s="2">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2">
+        <v>33</v>
+      </c>
+      <c r="E17" s="2">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3">
+        <v>34</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2">
+        <v>35</v>
+      </c>
+      <c r="E19" s="2">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="2">
+        <v>38</v>
+      </c>
+      <c r="E20" s="2">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="3">
+        <v>40</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2">
+        <v>40</v>
+      </c>
+      <c r="E22" s="2">
+        <v>2</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="2">
+        <v>42</v>
+      </c>
+      <c r="E23" s="2">
+        <v>2</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="2">
+        <v>42</v>
+      </c>
+      <c r="E24" s="2">
+        <v>2</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="2">
+        <v>44</v>
+      </c>
+      <c r="E25" s="2">
+        <v>2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="2">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2">
+        <v>2</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="2">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2">
+        <v>2</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D28" s="2">
+        <v>47</v>
+      </c>
+      <c r="E28" s="2">
+        <v>2</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" s="2">
+        <v>48</v>
+      </c>
+      <c r="E29" s="2">
+        <v>2</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" s="2">
+        <v>52</v>
+      </c>
+      <c r="E30" s="2">
+        <v>2</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" s="2">
+        <v>54</v>
+      </c>
+      <c r="E31" s="2">
+        <v>2</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="2">
+        <v>55</v>
+      </c>
+      <c r="E32" s="2">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="2">
+        <v>55</v>
+      </c>
+      <c r="E33" s="2">
+        <v>2</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="2">
+        <v>55</v>
+      </c>
+      <c r="E34" s="2">
+        <v>2</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="3">
+        <v>55</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1</v>
+      </c>
+      <c r="G35" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="2">
+        <v>55</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D37" s="2">
+        <v>59</v>
+      </c>
+      <c r="E37" s="2">
+        <v>2</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D38" s="3">
+        <v>60</v>
+      </c>
+      <c r="E38" s="3">
+        <v>2</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2">
+        <v>60</v>
+      </c>
+      <c r="E39" s="2">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D40" s="2">
+        <v>63</v>
+      </c>
+      <c r="E40" s="2">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D41" s="2">
+        <v>63</v>
+      </c>
+      <c r="E41" s="2">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2">
+        <v>1</v>
+      </c>
+      <c r="G41" s="4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="2">
+        <v>65</v>
+      </c>
+      <c r="E42" s="2">
+        <v>2</v>
+      </c>
+      <c r="F42" s="2">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="2">
+        <v>72</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D44" s="2">
+        <v>72</v>
+      </c>
+      <c r="E44" s="2">
+        <v>2</v>
+      </c>
+      <c r="F44" s="2">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="2">
+        <v>79</v>
+      </c>
+      <c r="E45" s="2">
+        <v>2</v>
+      </c>
+      <c r="F45" s="2">
+        <v>1</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="2">
+        <v>80</v>
+      </c>
+      <c r="E46" s="2">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="2">
+        <v>80</v>
+      </c>
+      <c r="E47" s="2">
+        <v>2</v>
+      </c>
+      <c r="F47" s="2">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="2">
+        <v>87</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2</v>
+      </c>
+      <c r="F48" s="2">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" s="3">
+        <v>88</v>
+      </c>
+      <c r="E49" s="2">
+        <v>2</v>
+      </c>
+      <c r="F49" s="2">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="3">
+        <v>91</v>
+      </c>
+      <c r="E50" s="2">
+        <v>2</v>
+      </c>
+      <c r="F50" s="2">
+        <v>1</v>
+      </c>
+      <c r="G50" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D51" s="2">
+        <v>102</v>
+      </c>
+      <c r="E51" s="2">
+        <v>2</v>
+      </c>
+      <c r="F51" s="2">
+        <v>1</v>
+      </c>
+      <c r="G51" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="2">
+        <v>107</v>
+      </c>
+      <c r="E52" s="2">
+        <v>2</v>
+      </c>
+      <c r="F52" s="2">
+        <v>1</v>
+      </c>
+      <c r="G52" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="2">
+        <v>109</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2</v>
+      </c>
+      <c r="F53" s="2">
+        <v>1</v>
+      </c>
+      <c r="G53" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D54" s="2">
+        <v>109</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2</v>
+      </c>
+      <c r="F54" s="2">
+        <v>1</v>
+      </c>
+      <c r="G54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="2">
+        <v>112</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2</v>
+      </c>
+      <c r="F55" s="2">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D56" s="2">
+        <v>113</v>
+      </c>
+      <c r="E56" s="2">
+        <v>2</v>
+      </c>
+      <c r="F56" s="2">
+        <v>1</v>
+      </c>
+      <c r="G56" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D57" s="2">
+        <v>113</v>
+      </c>
+      <c r="E57" s="2">
+        <v>2</v>
+      </c>
+      <c r="F57" s="2">
+        <v>1</v>
+      </c>
+      <c r="G57" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="2">
+        <v>115</v>
+      </c>
+      <c r="E58" s="2">
+        <v>2</v>
+      </c>
+      <c r="F58" s="2">
+        <v>1</v>
+      </c>
+      <c r="G58" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D59" s="2">
+        <v>132</v>
+      </c>
+      <c r="E59" s="2">
+        <v>2</v>
+      </c>
+      <c r="F59" s="2">
+        <v>1</v>
+      </c>
+      <c r="G59" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D60" s="2">
+        <v>135</v>
+      </c>
+      <c r="E60" s="2">
+        <v>2</v>
+      </c>
+      <c r="F60" s="2">
+        <v>1</v>
+      </c>
+      <c r="G60" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="2">
+        <v>136</v>
+      </c>
+      <c r="E61" s="2">
+        <v>2</v>
+      </c>
+      <c r="F61" s="2">
+        <v>1</v>
+      </c>
+      <c r="G61" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D62" s="2">
+        <v>136</v>
+      </c>
+      <c r="E62" s="2">
+        <v>2</v>
+      </c>
+      <c r="F62" s="2">
+        <v>1</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D63" s="2">
+        <v>145</v>
+      </c>
+      <c r="E63" s="2">
+        <v>2</v>
+      </c>
+      <c r="F63" s="2">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64" s="2">
+        <v>161</v>
+      </c>
+      <c r="E64" s="2">
+        <v>2</v>
+      </c>
+      <c r="F64" s="2">
+        <v>1</v>
+      </c>
+      <c r="G64" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D65" s="2">
+        <v>167</v>
+      </c>
+      <c r="E65" s="2">
+        <v>2</v>
+      </c>
+      <c r="F65" s="2">
+        <v>1</v>
+      </c>
+      <c r="G65" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D66" s="2">
+        <v>179</v>
+      </c>
+      <c r="E66" s="2">
+        <v>2</v>
+      </c>
+      <c r="F66" s="2">
+        <v>1</v>
+      </c>
+      <c r="G66" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="2">
+        <v>189</v>
+      </c>
+      <c r="E67" s="2">
+        <v>2</v>
+      </c>
+      <c r="F67" s="2">
+        <v>1</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D68" s="2">
+        <v>204</v>
+      </c>
+      <c r="E68" s="2">
+        <v>2</v>
+      </c>
+      <c r="F68" s="2">
+        <v>1</v>
+      </c>
+      <c r="G68" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D69" s="2">
+        <v>206</v>
+      </c>
+      <c r="E69" s="2">
+        <v>2</v>
+      </c>
+      <c r="F69" s="2">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="2">
+        <v>206</v>
+      </c>
+      <c r="E70" s="2">
+        <v>2</v>
+      </c>
+      <c r="F70" s="2">
+        <v>1</v>
+      </c>
+      <c r="G70" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" s="2">
+        <v>214</v>
+      </c>
+      <c r="E71" s="2">
+        <v>2</v>
+      </c>
+      <c r="F71" s="2">
+        <v>1</v>
+      </c>
+      <c r="G71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D72" s="2">
+        <v>216</v>
+      </c>
+      <c r="E72" s="2">
+        <v>2</v>
+      </c>
+      <c r="F72" s="2">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D73" s="2">
+        <v>220</v>
+      </c>
+      <c r="E73" s="2">
+        <v>2</v>
+      </c>
+      <c r="F73" s="2">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D74" s="2">
+        <v>226</v>
+      </c>
+      <c r="E74" s="2">
+        <v>2</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="D75" s="2">
+        <v>226</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D76" s="2">
+        <v>233</v>
+      </c>
+      <c r="E76" s="2">
+        <v>2</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="2">
+        <v>249</v>
+      </c>
+      <c r="E77" s="2">
+        <v>2</v>
+      </c>
+      <c r="F77" s="2">
+        <v>1</v>
+      </c>
+      <c r="G77" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" s="2">
+        <v>266</v>
+      </c>
+      <c r="E78" s="2">
+        <v>2</v>
+      </c>
+      <c r="F78" s="2">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="2">
+        <v>274</v>
+      </c>
+      <c r="E79" s="2">
+        <v>2</v>
+      </c>
+      <c r="F79" s="2">
+        <v>1</v>
+      </c>
+      <c r="G79" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D80" s="2">
+        <v>275</v>
+      </c>
+      <c r="E80" s="2">
+        <v>2</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D81" s="2">
+        <v>288</v>
+      </c>
+      <c r="E81" s="2">
+        <v>2</v>
+      </c>
+      <c r="F81" s="2">
+        <v>1</v>
+      </c>
+      <c r="G81" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D82" s="2">
+        <v>310</v>
+      </c>
+      <c r="E82" s="2">
+        <v>2</v>
+      </c>
+      <c r="F82" s="2">
+        <v>1</v>
+      </c>
+      <c r="G82" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" s="2">
+        <v>315</v>
+      </c>
+      <c r="E83" s="2">
+        <v>2</v>
+      </c>
+      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="G83" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D84" s="2">
+        <v>332</v>
+      </c>
+      <c r="E84" s="2">
+        <v>2</v>
+      </c>
+      <c r="F84" s="2">
+        <v>1</v>
+      </c>
+      <c r="G84" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D85" s="2">
+        <v>342</v>
+      </c>
+      <c r="E85" s="2">
+        <v>2</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1</v>
+      </c>
+      <c r="G85" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D86" s="2">
+        <v>356</v>
+      </c>
+      <c r="E86" s="2">
+        <v>2</v>
+      </c>
+      <c r="F86" s="2">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D87" s="2">
+        <v>356</v>
+      </c>
+      <c r="E87" s="2">
+        <v>2</v>
+      </c>
+      <c r="F87" s="2">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="2">
+        <v>366</v>
+      </c>
+      <c r="E88" s="2">
+        <v>2</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1</v>
+      </c>
+      <c r="G88" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D89" s="2">
+        <v>368</v>
+      </c>
+      <c r="E89" s="2">
+        <v>2</v>
+      </c>
+      <c r="F89" s="2">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D90" s="2">
+        <v>370</v>
+      </c>
+      <c r="E90" s="2">
+        <v>2</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="D91" s="2">
+        <v>382</v>
+      </c>
+      <c r="E91" s="2">
+        <v>2</v>
+      </c>
+      <c r="F91" s="2">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="2">
+        <v>386</v>
+      </c>
+      <c r="E92" s="2">
+        <v>2</v>
+      </c>
+      <c r="F92" s="2">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="2">
+        <v>401</v>
+      </c>
+      <c r="E93" s="2">
+        <v>2</v>
+      </c>
+      <c r="F93" s="2">
+        <v>1</v>
+      </c>
+      <c r="G93" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D94" s="2">
+        <v>425</v>
+      </c>
+      <c r="E94" s="2">
+        <v>2</v>
+      </c>
+      <c r="F94" s="2">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D95" s="2">
+        <v>427</v>
+      </c>
+      <c r="E95" s="2">
+        <v>2</v>
+      </c>
+      <c r="F95" s="2">
+        <v>1</v>
+      </c>
+      <c r="G95" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D96" s="2">
+        <v>443</v>
+      </c>
+      <c r="E96" s="2">
+        <v>2</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1</v>
+      </c>
+      <c r="G96" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="2">
+        <v>451</v>
+      </c>
+      <c r="E97" s="2">
+        <v>2</v>
+      </c>
+      <c r="F97" s="2">
+        <v>1</v>
+      </c>
+      <c r="G97" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D98" s="2">
+        <v>451</v>
+      </c>
+      <c r="E98" s="2">
+        <v>2</v>
+      </c>
+      <c r="F98" s="2">
+        <v>1</v>
+      </c>
+      <c r="G98" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D99" s="2">
+        <v>463</v>
+      </c>
+      <c r="E99" s="2">
+        <v>2</v>
+      </c>
+      <c r="F99" s="2">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D100" s="2">
+        <v>464</v>
+      </c>
+      <c r="E100" s="2">
+        <v>2</v>
+      </c>
+      <c r="F100" s="2">
+        <v>1</v>
+      </c>
+      <c r="G100" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D101" s="2">
+        <v>469</v>
+      </c>
+      <c r="E101" s="2">
+        <v>2</v>
+      </c>
+      <c r="F101" s="2">
+        <v>1</v>
+      </c>
+      <c r="G101" s="2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G101">
+    <sortState ref="A2:G101">
+      <sortCondition ref="D1:D101"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>